--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3638F656-2B3F-4FDB-A691-5CF246A15019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FFD224-F604-415F-B2EE-D7A0614E0C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72810" yWindow="-10815" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20295" yWindow="-20640" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="23">
   <si>
     <t>Type</t>
   </si>
@@ -109,6 +109,12 @@
   <si>
     <t>Flexible Load</t>
   </si>
+  <si>
+    <t>Pc_</t>
+  </si>
+  <si>
+    <t>Qc_</t>
+  </si>
 </sst>
 </file>
 
@@ -123,12 +129,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,10 +155,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,14 +441,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -447,8 +461,14 @@
       <c r="D1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -461,8 +481,14 @@
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="4">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -475,8 +501,14 @@
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -489,8 +521,14 @@
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -503,8 +541,14 @@
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -517,8 +561,14 @@
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -531,8 +581,14 @@
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="4">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -545,8 +601,14 @@
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="4">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -559,8 +621,14 @@
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -573,8 +641,14 @@
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -587,8 +661,14 @@
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="4">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -601,8 +681,14 @@
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -615,8 +701,14 @@
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -629,8 +721,14 @@
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -643,8 +741,14 @@
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -657,8 +761,14 @@
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -671,8 +781,14 @@
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -685,8 +801,14 @@
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -699,8 +821,14 @@
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -713,8 +841,14 @@
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -727,8 +861,14 @@
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -741,8 +881,14 @@
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -755,8 +901,14 @@
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -769,8 +921,14 @@
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="4">
+        <v>16.8</v>
+      </c>
+      <c r="F24" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -783,8 +941,14 @@
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="4">
+        <v>16.8</v>
+      </c>
+      <c r="F25" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -797,8 +961,14 @@
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -811,8 +981,14 @@
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -825,8 +1001,14 @@
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -839,8 +1021,14 @@
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="F29" s="4">
+        <v>2.8000000000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -853,8 +1041,14 @@
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="4">
+        <v>8</v>
+      </c>
+      <c r="F30" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -867,8 +1061,14 @@
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="4">
+        <v>6</v>
+      </c>
+      <c r="F31" s="4">
+        <v>2.8000000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -881,8 +1081,14 @@
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="F32" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -895,12 +1101,18 @@
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FFD224-F604-415F-B2EE-D7A0614E0C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E4449F-1B44-4BB5-B025-7F7EB23EE700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20295" yWindow="-20640" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -1036,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC75F9C-7AEC-4C1C-AEBF-2AC6E6D2155D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455975B8-8B6E-467C-ABC1-E0B04925A845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -1339,7 +1339,7 @@
         <v>0.30423493001908397</v>
       </c>
       <c r="AZ2">
-        <f t="shared" ref="AD2:AZ2" si="0">$AB2*AA2</f>
+        <f t="shared" ref="AZ2" si="0">$AB2*AA2</f>
         <v>0</v>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>32</v>
       </c>
@@ -34658,106 +34658,6 @@
       </c>
       <c r="AA385" s="1">
         <v>0.42119773420853601</v>
-      </c>
-      <c r="AB385">
-        <f t="shared" ref="AB323:AB385" ca="1" si="7">RANDBETWEEN(95,105)/100</f>
-        <v>0.98</v>
-      </c>
-      <c r="AC385">
-        <f t="shared" ref="AC323:AC385" ca="1" si="8">$AB385*D385</f>
-        <v>0.41436026058740344</v>
-      </c>
-      <c r="AD385">
-        <f t="shared" ref="AD323:AD385" ca="1" si="9">$AB385*E385</f>
-        <v>0.37748444863403641</v>
-      </c>
-      <c r="AE385">
-        <f t="shared" ref="AE323:AE385" ca="1" si="10">$AB385*F385</f>
-        <v>0.35171354390834303</v>
-      </c>
-      <c r="AF385">
-        <f t="shared" ref="AF323:AF385" ca="1" si="11">$AB385*G385</f>
-        <v>0.37551991138465385</v>
-      </c>
-      <c r="AG385">
-        <f t="shared" ref="AG323:AG385" ca="1" si="12">$AB385*H385</f>
-        <v>0.38496261689782052</v>
-      </c>
-      <c r="AH385">
-        <f t="shared" ref="AH323:AH385" ca="1" si="13">$AB385*I385</f>
-        <v>0.39145832721656248</v>
-      </c>
-      <c r="AI385">
-        <f t="shared" ref="AI323:AI385" ca="1" si="14">$AB385*J385</f>
-        <v>0.42829605734978399</v>
-      </c>
-      <c r="AJ385">
-        <f t="shared" ref="AJ323:AJ385" ca="1" si="15">$AB385*K385</f>
-        <v>0.55466326343146666</v>
-      </c>
-      <c r="AK385">
-        <f t="shared" ref="AK323:AK385" ca="1" si="16">$AB385*L385</f>
-        <v>0.57764207479572349</v>
-      </c>
-      <c r="AL385">
-        <f t="shared" ref="AL323:AL385" ca="1" si="17">$AB385*M385</f>
-        <v>0.60402173837297457</v>
-      </c>
-      <c r="AM385">
-        <f t="shared" ref="AM323:AM385" ca="1" si="18">$AB385*N385</f>
-        <v>0.57091327075743148</v>
-      </c>
-      <c r="AN385">
-        <f t="shared" ref="AN323:AN385" ca="1" si="19">$AB385*O385</f>
-        <v>0.61870171570721899</v>
-      </c>
-      <c r="AO385">
-        <f t="shared" ref="AO323:AO385" ca="1" si="20">$AB385*P385</f>
-        <v>0.5910113093245053</v>
-      </c>
-      <c r="AP385">
-        <f t="shared" ref="AP323:AP385" ca="1" si="21">$AB385*Q385</f>
-        <v>0.59193363507312824</v>
-      </c>
-      <c r="AQ385">
-        <f t="shared" ref="AQ323:AQ385" ca="1" si="22">$AB385*R385</f>
-        <v>0.53085843433776814</v>
-      </c>
-      <c r="AR385">
-        <f t="shared" ref="AR323:AR385" ca="1" si="23">$AB385*S385</f>
-        <v>0.54029389525090676</v>
-      </c>
-      <c r="AS385">
-        <f t="shared" ref="AS323:AS385" ca="1" si="24">$AB385*T385</f>
-        <v>0.5173098116703525</v>
-      </c>
-      <c r="AT385">
-        <f t="shared" ref="AT323:AT385" ca="1" si="25">$AB385*U385</f>
-        <v>0.51708889717824391</v>
-      </c>
-      <c r="AU385">
-        <f t="shared" ref="AU323:AU385" ca="1" si="26">$AB385*V385</f>
-        <v>0.51616710392953902</v>
-      </c>
-      <c r="AV385">
-        <f t="shared" ref="AV323:AV385" ca="1" si="27">$AB385*W385</f>
-        <v>0.53787148232046411</v>
-      </c>
-      <c r="AW385">
-        <f t="shared" ref="AW323:AW385" ca="1" si="28">$AB385*X385</f>
-        <v>0.53379996595701606</v>
-      </c>
-      <c r="AX385">
-        <f t="shared" ref="AX323:AX385" ca="1" si="29">$AB385*Y385</f>
-        <v>0.49771568732174559</v>
-      </c>
-      <c r="AY385">
-        <f t="shared" ref="AY323:AY385" ca="1" si="30">$AB385*Z385</f>
-        <v>0.43795392727218357</v>
-      </c>
-      <c r="AZ385">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.41277377952436528</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455975B8-8B6E-467C-ABC1-E0B04925A845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF94B4E-1449-4897-B761-D3B45613BFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -1167,10 +1167,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206E5596-3B52-412C-A9A4-71C002FACF4D}">
-  <dimension ref="A1:AZ385"/>
+  <dimension ref="A1:AA385"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1252,11 +1252,8 @@
       <c r="AA1">
         <v>23</v>
       </c>
-      <c r="AZ1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1338,12 +1335,8 @@
       <c r="AA2" s="1">
         <v>0.30423493001908397</v>
       </c>
-      <c r="AZ2">
-        <f t="shared" ref="AZ2" si="0">$AB2*AA2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1425,12 +1418,8 @@
       <c r="AA3" s="1">
         <v>0.12215315627057644</v>
       </c>
-      <c r="AZ3">
-        <f t="shared" ref="AZ3:AZ66" si="1">$AB3*AA3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1512,12 +1501,8 @@
       <c r="AA4" s="1">
         <v>0.28807338371711955</v>
       </c>
-      <c r="AZ4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1599,12 +1584,8 @@
       <c r="AA5" s="1">
         <v>5.140697371227413E-2</v>
       </c>
-      <c r="AZ5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1686,12 +1667,8 @@
       <c r="AA6" s="1">
         <v>0.31988431141736134</v>
       </c>
-      <c r="AZ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1773,12 +1750,8 @@
       <c r="AA7" s="1">
         <v>0.45601221277188941</v>
       </c>
-      <c r="AZ7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1860,12 +1833,8 @@
       <c r="AA8" s="1">
         <v>0.23212504519623703</v>
       </c>
-      <c r="AZ8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1947,12 +1916,8 @@
       <c r="AA9" s="1">
         <v>0.16447266993333343</v>
       </c>
-      <c r="AZ9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2034,12 +1999,8 @@
       <c r="AA10" s="1">
         <v>0.14884669085844837</v>
       </c>
-      <c r="AZ10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2121,12 +2082,8 @@
       <c r="AA11" s="1">
         <v>0.21182466623223417</v>
       </c>
-      <c r="AZ11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2208,12 +2165,8 @@
       <c r="AA12" s="1">
         <v>8.8097283050149661E-2</v>
       </c>
-      <c r="AZ12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2295,12 +2248,8 @@
       <c r="AA13" s="1">
         <v>0.37751283536620156</v>
       </c>
-      <c r="AZ13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2382,12 +2331,8 @@
       <c r="AA14" s="1">
         <v>0.71253728546098483</v>
       </c>
-      <c r="AZ14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2469,12 +2414,8 @@
       <c r="AA15" s="1">
         <v>0.29519824892940821</v>
       </c>
-      <c r="AZ15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2556,12 +2497,8 @@
       <c r="AA16" s="1">
         <v>0.1208807275594246</v>
       </c>
-      <c r="AZ16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2643,12 +2580,8 @@
       <c r="AA17" s="1">
         <v>0.29717043793976544</v>
       </c>
-      <c r="AZ17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2730,12 +2663,8 @@
       <c r="AA18" s="1">
         <v>5.090787688011613E-2</v>
       </c>
-      <c r="AZ18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2817,12 +2746,8 @@
       <c r="AA19" s="1">
         <v>0.33620493955090019</v>
       </c>
-      <c r="AZ19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2904,12 +2829,8 @@
       <c r="AA20" s="1">
         <v>0.47011568326998909</v>
       </c>
-      <c r="AZ20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2991,12 +2912,8 @@
       <c r="AA21" s="1">
         <v>0.22743565034378779</v>
       </c>
-      <c r="AZ21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3078,12 +2995,8 @@
       <c r="AA22" s="1">
         <v>0.16275941295486118</v>
       </c>
-      <c r="AZ22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3165,12 +3078,8 @@
       <c r="AA23" s="1">
         <v>0.15970009540021024</v>
       </c>
-      <c r="AZ23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3252,12 +3161,8 @@
       <c r="AA24" s="1">
         <v>0.21390137864627567</v>
       </c>
-      <c r="AZ24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3339,12 +3244,8 @@
       <c r="AA25" s="1">
         <v>8.3063152590141104E-2</v>
       </c>
-      <c r="AZ25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3426,12 +3327,8 @@
       <c r="AA26" s="1">
         <v>0.38918849006824902</v>
       </c>
-      <c r="AZ26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3513,12 +3410,8 @@
       <c r="AA27" s="1">
         <v>0.764493129192515</v>
       </c>
-      <c r="AZ27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3600,12 +3493,8 @@
       <c r="AA28" s="1">
         <v>0.31025938407886783</v>
       </c>
-      <c r="AZ28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3687,12 +3576,8 @@
       <c r="AA29" s="1">
         <v>0.12724287111518379</v>
       </c>
-      <c r="AZ29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3774,12 +3659,8 @@
       <c r="AA30" s="1">
         <v>0.28807338371711955</v>
       </c>
-      <c r="AZ30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3861,12 +3742,8 @@
       <c r="AA31" s="1">
         <v>5.240516737659013E-2</v>
       </c>
-      <c r="AZ31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3948,12 +3825,8 @@
       <c r="AA32" s="1">
         <v>0.33620493955090019</v>
       </c>
-      <c r="AZ32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4035,12 +3908,8 @@
       <c r="AA33" s="1">
         <v>0.47951799693538888</v>
       </c>
-      <c r="AZ33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -4122,12 +3991,8 @@
       <c r="AA34" s="1">
         <v>0.3164043272198474</v>
       </c>
-      <c r="AZ34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4209,12 +4074,8 @@
       <c r="AA35" s="1">
         <v>0.13497923767898695</v>
       </c>
-      <c r="AZ35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4296,12 +4157,8 @@
       <c r="AA36" s="1">
         <v>0.32167183731275839</v>
       </c>
-      <c r="AZ36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>4</v>
       </c>
@@ -4383,12 +4240,8 @@
       <c r="AA37" s="1">
         <v>5.1387009838987807E-2</v>
       </c>
-      <c r="AZ37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4470,12 +4323,8 @@
       <c r="AA38" s="1">
         <v>0.33607437452583194</v>
       </c>
-      <c r="AZ38">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4557,12 +4406,8 @@
       <c r="AA39" s="1">
         <v>0.47914190438877291</v>
       </c>
-      <c r="AZ39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4644,12 +4489,8 @@
       <c r="AA40" s="1">
         <v>0.25360247362045452</v>
       </c>
-      <c r="AZ40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4731,12 +4572,8 @@
       <c r="AA41" s="1">
         <v>0.17105157673066676</v>
       </c>
-      <c r="AZ41">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>9</v>
       </c>
@@ -4818,12 +4655,8 @@
       <c r="AA42" s="1">
         <v>0.15480055849278632</v>
       </c>
-      <c r="AZ42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>10</v>
       </c>
@@ -4905,12 +4738,8 @@
       <c r="AA43" s="1">
         <v>0.20949874832850765</v>
       </c>
-      <c r="AZ43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>11</v>
       </c>
@@ -4992,12 +4821,8 @@
       <c r="AA44" s="1">
         <v>9.1621174372155653E-2</v>
       </c>
-      <c r="AZ44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>12</v>
       </c>
@@ -5079,12 +4904,8 @@
       <c r="AA45" s="1">
         <v>0.40070846937426924</v>
       </c>
-      <c r="AZ45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>13</v>
       </c>
@@ -5166,12 +4987,8 @@
       <c r="AA46" s="1">
         <v>0.7796345465085609</v>
       </c>
-      <c r="AZ46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14</v>
       </c>
@@ -5253,12 +5070,8 @@
       <c r="AA47" s="1">
         <v>0.32266975944202259</v>
       </c>
-      <c r="AZ47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>15</v>
       </c>
@@ -5340,12 +5153,8 @@
       <c r="AA48" s="1">
         <v>0.12968593424059532</v>
       </c>
-      <c r="AZ48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>16</v>
       </c>
@@ -5427,12 +5236,8 @@
       <c r="AA49" s="1">
         <v>0.31851819184890778</v>
       </c>
-      <c r="AZ49">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>17</v>
       </c>
@@ -5514,12 +5319,8 @@
       <c r="AA50" s="1">
         <v>4.9310767017210523E-2</v>
       </c>
-      <c r="AZ50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>18</v>
       </c>
@@ -5601,12 +5402,8 @@
       <c r="AA51" s="1">
         <v>0.35644251843648839</v>
       </c>
-      <c r="AZ51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>19</v>
       </c>
@@ -5688,12 +5485,8 @@
       <c r="AA52" s="1">
         <v>0.51336632613082811</v>
       </c>
-      <c r="AZ52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>20</v>
       </c>
@@ -5775,12 +5568,8 @@
       <c r="AA53" s="1">
         <v>0.23653307635753931</v>
       </c>
-      <c r="AZ53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>21</v>
       </c>
@@ -5862,12 +5651,8 @@
       <c r="AA54" s="1">
         <v>0.17283336398827787</v>
       </c>
-      <c r="AZ54">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>22</v>
       </c>
@@ -5949,12 +5734,8 @@
       <c r="AA55" s="1">
         <v>0.16286308758095228</v>
       </c>
-      <c r="AZ55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>23</v>
       </c>
@@ -6036,12 +5817,8 @@
       <c r="AA56" s="1">
         <v>0.213818310149714</v>
       </c>
-      <c r="AZ56">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>24</v>
       </c>
@@ -6123,12 +5900,8 @@
       <c r="AA57" s="1">
         <v>8.2895348241474168E-2</v>
       </c>
-      <c r="AZ57">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>25</v>
       </c>
@@ -6210,12 +5983,8 @@
       <c r="AA58" s="1">
         <v>0.40880358996768879</v>
       </c>
-      <c r="AZ58">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>26</v>
       </c>
@@ -6297,12 +6066,8 @@
       <c r="AA59" s="1">
         <v>0.81051116221187025</v>
       </c>
-      <c r="AZ59">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>27</v>
       </c>
@@ -6384,12 +6149,8 @@
       <c r="AA60" s="1">
         <v>0.3070061788865846</v>
       </c>
-      <c r="AZ60">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>28</v>
       </c>
@@ -6471,12 +6232,8 @@
       <c r="AA61" s="1">
         <v>0.12703928252139948</v>
       </c>
-      <c r="AZ61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>29</v>
       </c>
@@ -6558,12 +6315,8 @@
       <c r="AA62" s="1">
         <v>0.30905725545735607</v>
       </c>
-      <c r="AZ62">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>30</v>
       </c>
@@ -6645,12 +6398,8 @@
       <c r="AA63" s="1">
         <v>5.0867949133543484E-2</v>
       </c>
-      <c r="AZ63">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>31</v>
       </c>
@@ -6732,12 +6481,8 @@
       <c r="AA64" s="1">
         <v>0.32589030257050366</v>
       </c>
-      <c r="AZ64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>32</v>
       </c>
@@ -6819,12 +6564,8 @@
       <c r="AA65" s="1">
         <v>0.47425270128276498</v>
       </c>
-      <c r="AZ65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6906,12 +6647,8 @@
       <c r="AA66" s="1">
         <v>0.28043833648293781</v>
       </c>
-      <c r="AZ66">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6993,12 +6730,8 @@
       <c r="AA67" s="1">
         <v>0.12594499382980892</v>
       </c>
-      <c r="AZ67">
-        <f t="shared" ref="AZ67:AZ130" si="2">$AB67*AA67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>3</v>
       </c>
@@ -7080,12 +6813,8 @@
       <c r="AA68" s="1">
         <v>0.30014214231916309</v>
       </c>
-      <c r="AZ68">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>4</v>
       </c>
@@ -7167,12 +6896,8 @@
       <c r="AA69" s="1">
         <v>5.1357064029058326E-2</v>
       </c>
-      <c r="AZ69">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>5</v>
       </c>
@@ -7254,12 +6979,8 @@
       <c r="AA70" s="1">
         <v>0.3134866251890141</v>
       </c>
-      <c r="AZ70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>6</v>
       </c>
@@ -7341,12 +7062,8 @@
       <c r="AA71" s="1">
         <v>0.47914190438877291</v>
       </c>
-      <c r="AZ71">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>7</v>
       </c>
@@ -7428,12 +7145,8 @@
       <c r="AA72" s="1">
         <v>0.22518474081461215</v>
       </c>
-      <c r="AZ72">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7515,12 +7228,8 @@
       <c r="AA73" s="1">
         <v>0.1729361594069862</v>
       </c>
-      <c r="AZ73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>9</v>
       </c>
@@ -7602,12 +7311,8 @@
       <c r="AA74" s="1">
         <v>0.14435028040543274</v>
       </c>
-      <c r="AZ74">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>10</v>
       </c>
@@ -7689,12 +7394,8 @@
       <c r="AA75" s="1">
         <v>0.2035178165760681</v>
       </c>
-      <c r="AZ75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>11</v>
       </c>
@@ -7776,12 +7477,8 @@
       <c r="AA76" s="1">
         <v>7.8112924304466036E-2</v>
       </c>
-      <c r="AZ76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>12</v>
       </c>
@@ -7863,12 +7560,8 @@
       <c r="AA77" s="1">
         <v>0.38903281467222173</v>
       </c>
-      <c r="AZ77">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>13</v>
       </c>
@@ -7950,12 +7643,8 @@
       <c r="AA78" s="1">
         <v>0.70556035787417926</v>
       </c>
-      <c r="AZ78">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14</v>
       </c>
@@ -8037,12 +7726,8 @@
       <c r="AA79" s="1">
         <v>0.29224626644011414</v>
       </c>
-      <c r="AZ79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>15</v>
       </c>
@@ -8124,12 +7809,8 @@
       <c r="AA80" s="1">
         <v>0.13093291437752413</v>
       </c>
-      <c r="AZ80">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>16</v>
       </c>
@@ -8211,12 +7892,8 @@
       <c r="AA81" s="1">
         <v>0.29122702918097015</v>
       </c>
-      <c r="AZ81">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>17</v>
       </c>
@@ -8298,12 +7975,8 @@
       <c r="AA82" s="1">
         <v>5.0378834238028643E-2</v>
       </c>
-      <c r="AZ82">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>18</v>
       </c>
@@ -8385,12 +8058,8 @@
       <c r="AA83" s="1">
         <v>0.33587852698822945</v>
       </c>
-      <c r="AZ83">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>19</v>
       </c>
@@ -8472,12 +8141,8 @@
       <c r="AA84" s="1">
         <v>0.4422848348204057</v>
       </c>
-      <c r="AZ84">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>20</v>
       </c>
@@ -8559,12 +8224,8 @@
       <c r="AA85" s="1">
         <v>0.22748254429231229</v>
       </c>
-      <c r="AZ85">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>21</v>
       </c>
@@ -8646,12 +8307,8 @@
       <c r="AA86" s="1">
         <v>0.17629414308479177</v>
       </c>
-      <c r="AZ86">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>22</v>
       </c>
@@ -8733,12 +8390,8 @@
       <c r="AA87" s="1">
         <v>0.14890871031297273</v>
       </c>
-      <c r="AZ87">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>23</v>
       </c>
@@ -8820,12 +8473,8 @@
       <c r="AA88" s="1">
         <v>0.20555299474182878</v>
       </c>
-      <c r="AZ88">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>24</v>
       </c>
@@ -8907,12 +8556,8 @@
       <c r="AA89" s="1">
         <v>7.8112924304466036E-2</v>
       </c>
-      <c r="AZ89">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>25</v>
       </c>
@@ -8994,12 +8639,8 @@
       <c r="AA90" s="1">
         <v>0.38521876746955291</v>
       </c>
-      <c r="AZ90">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>26</v>
       </c>
@@ -9081,12 +8722,8 @@
       <c r="AA91" s="1">
         <v>0.72010799411900772</v>
       </c>
-      <c r="AZ91">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>27</v>
       </c>
@@ -9168,12 +8805,8 @@
       <c r="AA92" s="1">
         <v>0.29519824892940821</v>
       </c>
-      <c r="AZ92">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>28</v>
       </c>
@@ -9255,12 +8888,8 @@
       <c r="AA93" s="1">
         <v>0.1184631130082361</v>
       </c>
-      <c r="AZ93">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>29</v>
       </c>
@@ -9342,12 +8971,8 @@
       <c r="AA94" s="1">
         <v>0.30311384669856073</v>
       </c>
-      <c r="AZ94">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>30</v>
       </c>
@@ -9429,12 +9054,8 @@
       <c r="AA95" s="1">
         <v>4.9889719342513801E-2</v>
       </c>
-      <c r="AZ95">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>31</v>
       </c>
@@ -9516,12 +9137,8 @@
       <c r="AA96" s="1">
         <v>0.3134866251890141</v>
       </c>
-      <c r="AZ96">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>32</v>
       </c>
@@ -9603,12 +9220,8 @@
       <c r="AA97" s="1">
         <v>0.47914190438877291</v>
       </c>
-      <c r="AZ97">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9690,12 +9303,8 @@
       <c r="AA98" s="1">
         <v>0.40460512983649527</v>
       </c>
-      <c r="AZ98">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2</v>
       </c>
@@ -9777,12 +9386,8 @@
       <c r="AA99" s="1">
         <v>0.12531670023913216</v>
       </c>
-      <c r="AZ99">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>3</v>
       </c>
@@ -9864,12 +9469,8 @@
       <c r="AA100" s="1">
         <v>0.29869072399109714</v>
       </c>
-      <c r="AZ100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4</v>
       </c>
@@ -9951,12 +9552,8 @@
       <c r="AA101" s="1">
         <v>4.4140186966755215E-2</v>
       </c>
-      <c r="AZ101">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>5</v>
       </c>
@@ -10038,12 +9635,8 @@
       <c r="AA102" s="1">
         <v>0.31506655879445489</v>
       </c>
-      <c r="AZ102">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>6</v>
       </c>
@@ -10125,12 +9718,8 @@
       <c r="AA103" s="1">
         <v>0.44456052640476812</v>
       </c>
-      <c r="AZ103">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>7</v>
       </c>
@@ -10212,12 +9801,8 @@
       <c r="AA104" s="1">
         <v>0.24397437503436967</v>
       </c>
-      <c r="AZ104">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>8</v>
       </c>
@@ -10299,12 +9884,8 @@
       <c r="AA105" s="1">
         <v>0.15382663214631914</v>
       </c>
-      <c r="AZ105">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>9</v>
       </c>
@@ -10386,12 +9967,8 @@
       <c r="AA106" s="1">
         <v>0.14269317780774657</v>
       </c>
-      <c r="AZ106">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -10473,12 +10050,8 @@
       <c r="AA107" s="1">
         <v>0.21685736810291287</v>
       </c>
-      <c r="AZ107">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>11</v>
       </c>
@@ -10560,12 +10133,8 @@
       <c r="AA108" s="1">
         <v>7.9818120109252197E-2</v>
       </c>
-      <c r="AZ108">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>12</v>
       </c>
@@ -10647,12 +10216,8 @@
       <c r="AA109" s="1">
         <v>0.45025918839909279</v>
       </c>
-      <c r="AZ109">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>13</v>
       </c>
@@ -10734,12 +10299,8 @@
       <c r="AA110" s="1">
         <v>0.78440506467065618</v>
       </c>
-      <c r="AZ110">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>14</v>
       </c>
@@ -10821,12 +10382,8 @@
       <c r="AA111" s="1">
         <v>0.4349917738149664</v>
       </c>
-      <c r="AZ111">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>15</v>
       </c>
@@ -10908,12 +10465,8 @@
       <c r="AA112" s="1">
         <v>0.12151477012193317</v>
       </c>
-      <c r="AZ112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>16</v>
       </c>
@@ -10995,12 +10548,8 @@
       <c r="AA113" s="1">
         <v>0.29988121067334794</v>
       </c>
-      <c r="AZ113">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>17</v>
       </c>
@@ -11082,12 +10631,8 @@
       <c r="AA114" s="1">
         <v>4.4687934013653223E-2</v>
       </c>
-      <c r="AZ114">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>18</v>
       </c>
@@ -11169,12 +10714,8 @@
       <c r="AA115" s="1">
         <v>0.33018527981719359</v>
       </c>
-      <c r="AZ115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>19</v>
       </c>
@@ -11256,12 +10797,8 @@
       <c r="AA116" s="1">
         <v>0.42311155071818235</v>
       </c>
-      <c r="AZ116">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>20</v>
       </c>
@@ -11343,12 +10880,8 @@
       <c r="AA117" s="1">
         <v>0.23439270222739572</v>
       </c>
-      <c r="AZ117">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>21</v>
       </c>
@@ -11430,12 +10963,8 @@
       <c r="AA118" s="1">
         <v>0.15708373083840152</v>
       </c>
-      <c r="AZ118">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>22</v>
       </c>
@@ -11517,12 +11046,8 @@
       <c r="AA119" s="1">
         <v>0.14033793264830885</v>
       </c>
-      <c r="AZ119">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>23</v>
       </c>
@@ -11604,12 +11129,8 @@
       <c r="AA120" s="1">
         <v>0.19882125121158906</v>
       </c>
-      <c r="AZ120">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>24</v>
       </c>
@@ -11691,12 +11212,8 @@
       <c r="AA121" s="1">
         <v>7.9720383742063805E-2</v>
       </c>
-      <c r="AZ121">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>25</v>
       </c>
@@ -11778,12 +11295,8 @@
       <c r="AA122" s="1">
         <v>0.42271478599915069</v>
       </c>
-      <c r="AZ122">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>26</v>
       </c>
@@ -11865,12 +11378,8 @@
       <c r="AA123" s="1">
         <v>0.7719433123864361</v>
       </c>
-      <c r="AZ123">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>27</v>
       </c>
@@ -11952,12 +11461,8 @@
       <c r="AA124" s="1">
         <v>0.42260815392379569</v>
       </c>
-      <c r="AZ124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>28</v>
       </c>
@@ -12039,12 +11544,8 @@
       <c r="AA125" s="1">
         <v>0.12503041680988139</v>
       </c>
-      <c r="AZ125">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>29</v>
       </c>
@@ -12126,12 +11627,8 @@
       <c r="AA126" s="1">
         <v>0.30983513447948846</v>
       </c>
-      <c r="AZ126">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>30</v>
       </c>
@@ -12213,12 +11710,8 @@
       <c r="AA127" s="1">
         <v>4.7369169177349381E-2</v>
       </c>
-      <c r="AZ127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>31</v>
       </c>
@@ -12300,12 +11793,8 @@
       <c r="AA128" s="1">
         <v>0.29376889231153613</v>
       </c>
-      <c r="AZ128">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>32</v>
       </c>
@@ -12387,12 +11876,8 @@
       <c r="AA129" s="1">
         <v>0.40276293406267627</v>
       </c>
-      <c r="AZ129">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1</v>
       </c>
@@ -12474,12 +11959,8 @@
       <c r="AA130" s="1">
         <v>0.42689047219041887</v>
       </c>
-      <c r="AZ130">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>2</v>
       </c>
@@ -12561,12 +12042,8 @@
       <c r="AA131" s="1">
         <v>0.12033783871790973</v>
       </c>
-      <c r="AZ131">
-        <f t="shared" ref="AZ131:AZ194" si="3">$AB131*AA131</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>3</v>
       </c>
@@ -12648,12 +12125,8 @@
       <c r="AA132" s="1">
         <v>0.29665445719231714</v>
       </c>
-      <c r="AZ132">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12735,12 +12208,8 @@
       <c r="AA133" s="1">
         <v>4.2953112347665981E-2</v>
       </c>
-      <c r="AZ133">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12822,12 +12291,8 @@
       <c r="AA134" s="1">
         <v>0.3215536643614364</v>
       </c>
-      <c r="AZ134">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>6</v>
       </c>
@@ -12909,12 +12374,8 @@
       <c r="AA135" s="1">
         <v>0.44732388733607209</v>
       </c>
-      <c r="AZ135">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>7</v>
       </c>
@@ -12996,12 +12457,8 @@
       <c r="AA136" s="1">
         <v>0.21766051836345818</v>
       </c>
-      <c r="AZ136">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>8</v>
       </c>
@@ -13083,12 +12540,8 @@
       <c r="AA137" s="1">
         <v>0.13917647670381256</v>
       </c>
-      <c r="AZ137">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>9</v>
       </c>
@@ -13170,12 +12623,8 @@
       <c r="AA138" s="1">
         <v>0.13581314695342595</v>
       </c>
-      <c r="AZ138">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>10</v>
       </c>
@@ -13257,12 +12706,8 @@
       <c r="AA139" s="1">
         <v>0.18744030886223878</v>
       </c>
-      <c r="AZ139">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>11</v>
       </c>
@@ -13344,12 +12789,8 @@
       <c r="AA140" s="1">
         <v>7.5711443802736714E-2</v>
       </c>
-      <c r="AZ140">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>12</v>
       </c>
@@ -13431,12 +12872,8 @@
       <c r="AA141" s="1">
         <v>0.45877795420658402</v>
       </c>
-      <c r="AZ141">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>13</v>
       </c>
@@ -13518,12 +12955,8 @@
       <c r="AA142" s="1">
         <v>0.72691636268398796</v>
       </c>
-      <c r="AZ142">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>14</v>
       </c>
@@ -13605,12 +13038,8 @@
       <c r="AA143" s="1">
         <v>0.40804281413635179</v>
       </c>
-      <c r="AZ143">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>15</v>
       </c>
@@ -13692,12 +13121,8 @@
       <c r="AA144" s="1">
         <v>0.11968020682142257</v>
       </c>
-      <c r="AZ144">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>16</v>
       </c>
@@ -13779,12 +13204,8 @@
       <c r="AA145" s="1">
         <v>0.2817710283800931</v>
       </c>
-      <c r="AZ145">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>17</v>
       </c>
@@ -13866,12 +13287,8 @@
       <c r="AA146" s="1">
         <v>4.7180765681348061E-2</v>
       </c>
-      <c r="AZ146">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>18</v>
       </c>
@@ -13953,12 +13370,8 @@
       <c r="AA147" s="1">
         <v>0.3246823184506501</v>
       </c>
-      <c r="AZ147">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>19</v>
       </c>
@@ -14040,12 +13453,8 @@
       <c r="AA148" s="1">
         <v>0.4378654235287498</v>
       </c>
-      <c r="AZ148">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>20</v>
       </c>
@@ -14127,12 +13536,8 @@
       <c r="AA149" s="1">
         <v>0.2315525622208352</v>
       </c>
-      <c r="AZ149">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>21</v>
       </c>
@@ -14214,12 +13619,8 @@
       <c r="AA150" s="1">
         <v>0.15065394992841988</v>
       </c>
-      <c r="AZ150">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>22</v>
       </c>
@@ -14301,12 +13702,8 @@
       <c r="AA151" s="1">
         <v>0.13333519255883414</v>
       </c>
-      <c r="AZ151">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>23</v>
       </c>
@@ -14388,12 +13785,8 @@
       <c r="AA152" s="1">
         <v>0.2201848013021738</v>
       </c>
-      <c r="AZ152">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>24</v>
       </c>
@@ -14475,12 +13868,8 @@
       <c r="AA153" s="1">
         <v>7.5208128585683348E-2</v>
       </c>
-      <c r="AZ153">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>25</v>
       </c>
@@ -14562,12 +13951,8 @@
       <c r="AA154" s="1">
         <v>0.42885448722957481</v>
       </c>
-      <c r="AZ154">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>26</v>
       </c>
@@ -14649,12 +14034,8 @@
       <c r="AA155" s="1">
         <v>0.75957708235256871</v>
       </c>
-      <c r="AZ155">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>27</v>
       </c>
@@ -14736,12 +14117,8 @@
       <c r="AA156" s="1">
         <v>0.41003335984872546</v>
       </c>
-      <c r="AZ156">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>28</v>
       </c>
@@ -14823,12 +14200,8 @@
       <c r="AA157" s="1">
         <v>0.12746094767742908</v>
       </c>
-      <c r="AZ157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>29</v>
       </c>
@@ -14910,12 +14283,8 @@
       <c r="AA158" s="1">
         <v>0.31004400592124742</v>
       </c>
-      <c r="AZ158">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>30</v>
       </c>
@@ -14997,12 +14366,8 @@
       <c r="AA159" s="1">
         <v>4.6176909736852456E-2</v>
       </c>
-      <c r="AZ159">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>31</v>
       </c>
@@ -15084,12 +14449,8 @@
       <c r="AA160" s="1">
         <v>0.31071405402795677</v>
       </c>
-      <c r="AZ160">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>32</v>
       </c>
@@ -15171,12 +14532,8 @@
       <c r="AA161" s="1">
         <v>0.44091942255282457</v>
       </c>
-      <c r="AZ161">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>1</v>
       </c>
@@ -15258,12 +14615,8 @@
       <c r="AA162" s="1">
         <v>0.42965036203221812</v>
       </c>
-      <c r="AZ162">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2</v>
       </c>
@@ -15345,12 +14698,8 @@
       <c r="AA163" s="1">
         <v>0.12289737753343244</v>
       </c>
-      <c r="AZ163">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>3</v>
       </c>
@@ -15432,12 +14781,8 @@
       <c r="AA164" s="1">
         <v>0.28273252588643172</v>
       </c>
-      <c r="AZ164">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>4</v>
       </c>
@@ -15519,12 +14864,8 @@
       <c r="AA165" s="1">
         <v>4.083949069934821E-2</v>
       </c>
-      <c r="AZ165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>5</v>
       </c>
@@ -15606,12 +14947,8 @@
       <c r="AA166" s="1">
         <v>0.32221764217060544</v>
       </c>
-      <c r="AZ166">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>6</v>
       </c>
@@ -15693,12 +15030,8 @@
       <c r="AA167" s="1">
         <v>0.46171304926561546</v>
       </c>
-      <c r="AZ167">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>7</v>
       </c>
@@ -15780,12 +15113,8 @@
       <c r="AA168" s="1">
         <v>0.24146630603376001</v>
       </c>
-      <c r="AZ168">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>8</v>
       </c>
@@ -15867,12 +15196,8 @@
       <c r="AA169" s="1">
         <v>0.16428246479929443</v>
       </c>
-      <c r="AZ169">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>9</v>
       </c>
@@ -15954,12 +15279,8 @@
       <c r="AA170" s="1">
         <v>0.13144036344599996</v>
       </c>
-      <c r="AZ170">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>10</v>
       </c>
@@ -16041,12 +15362,8 @@
       <c r="AA171" s="1">
         <v>0.19702677154429635</v>
       </c>
-      <c r="AZ171">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>11</v>
       </c>
@@ -16128,12 +15445,8 @@
       <c r="AA172" s="1">
         <v>7.2314319481827663E-2</v>
       </c>
-      <c r="AZ172">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>12</v>
       </c>
@@ -16215,12 +15528,8 @@
       <c r="AA173" s="1">
         <v>0.46001998724932369</v>
       </c>
-      <c r="AZ173">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>13</v>
       </c>
@@ -16302,12 +15611,8 @@
       <c r="AA174" s="1">
         <v>0.72622447296762938</v>
       </c>
-      <c r="AZ174">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>14</v>
       </c>
@@ -16389,12 +15694,8 @@
       <c r="AA175" s="1">
         <v>0.4010627508493424</v>
       </c>
-      <c r="AZ175">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>15</v>
       </c>
@@ -16476,12 +15777,8 @@
       <c r="AA176" s="1">
         <v>0.12537432575955593</v>
       </c>
-      <c r="AZ176">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>16</v>
       </c>
@@ -16563,12 +15860,8 @@
       <c r="AA177" s="1">
         <v>0.31273459745725996</v>
       </c>
-      <c r="AZ177">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>17</v>
       </c>
@@ -16650,12 +15943,8 @@
       <c r="AA178" s="1">
         <v>4.4051037967967832E-2</v>
       </c>
-      <c r="AZ178">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>18</v>
       </c>
@@ -16737,12 +16026,8 @@
       <c r="AA179" s="1">
         <v>0.29278258429582177</v>
       </c>
-      <c r="AZ179">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>19</v>
       </c>
@@ -16824,12 +16109,8 @@
       <c r="AA180" s="1">
         <v>0.43040774612253258</v>
       </c>
-      <c r="AZ180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>20</v>
       </c>
@@ -16911,12 +16192,8 @@
       <c r="AA181" s="1">
         <v>0.22549174696111235</v>
       </c>
-      <c r="AZ181">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>21</v>
       </c>
@@ -16998,12 +16275,8 @@
       <c r="AA182" s="1">
         <v>0.14289138994230252</v>
       </c>
-      <c r="AZ182">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>22</v>
       </c>
@@ -17085,12 +16358,8 @@
       <c r="AA183" s="1">
         <v>0.13544434056330421</v>
       </c>
-      <c r="AZ183">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>23</v>
       </c>
@@ -17172,12 +16441,8 @@
       <c r="AA184" s="1">
         <v>0.21582499841669786</v>
       </c>
-      <c r="AZ184">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>24</v>
       </c>
@@ -17259,12 +16524,8 @@
       <c r="AA185" s="1">
         <v>8.3930712813533967E-2</v>
       </c>
-      <c r="AZ185">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>25</v>
       </c>
@@ -17346,12 +16607,8 @@
       <c r="AA186" s="1">
         <v>0.45973303128551724</v>
       </c>
-      <c r="AZ186">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>26</v>
       </c>
@@ -17433,12 +16690,8 @@
       <c r="AA187" s="1">
         <v>0.73190418906602639</v>
       </c>
-      <c r="AZ187">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>27</v>
       </c>
@@ -17520,12 +16773,8 @@
       <c r="AA188" s="1">
         <v>0.39427768777634509</v>
       </c>
-      <c r="AZ188">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>28</v>
       </c>
@@ -17607,12 +16856,8 @@
       <c r="AA189" s="1">
         <v>0.12672797661677199</v>
       </c>
-      <c r="AZ189">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>29</v>
       </c>
@@ -17694,12 +16939,8 @@
       <c r="AA190" s="1">
         <v>0.29363456677379773</v>
       </c>
-      <c r="AZ190">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>30</v>
       </c>
@@ -17781,12 +17022,8 @@
       <c r="AA191" s="1">
         <v>4.8685903486685111E-2</v>
       </c>
-      <c r="AZ191">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>31</v>
       </c>
@@ -17868,12 +17105,8 @@
       <c r="AA192" s="1">
         <v>0.31338468480191034</v>
       </c>
-      <c r="AZ192">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>32</v>
       </c>
@@ -17955,12 +17188,8 @@
       <c r="AA193" s="1">
         <v>0.45918880408260448</v>
       </c>
-      <c r="AZ193">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1</v>
       </c>
@@ -18042,12 +17271,8 @@
       <c r="AA194" s="1">
         <v>0.56850363147764293</v>
       </c>
-      <c r="AZ194">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>2</v>
       </c>
@@ -18129,12 +17354,8 @@
       <c r="AA195" s="1">
         <v>0.1409055153001664</v>
       </c>
-      <c r="AZ195">
-        <f t="shared" ref="AZ195:AZ258" si="4">$AB195*AA195</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>3</v>
       </c>
@@ -18216,12 +17437,8 @@
       <c r="AA196" s="1">
         <v>0.33597021620982936</v>
       </c>
-      <c r="AZ196">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>4</v>
       </c>
@@ -18303,12 +17520,8 @@
       <c r="AA197" s="1">
         <v>4.6885646565674503E-2</v>
       </c>
-      <c r="AZ197">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>5</v>
       </c>
@@ -18390,12 +17603,8 @@
       <c r="AA198" s="1">
         <v>0.32717567035626965</v>
       </c>
-      <c r="AZ198">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>6</v>
       </c>
@@ -18477,12 +17686,8 @@
       <c r="AA199" s="1">
         <v>0.45982461493547749</v>
       </c>
-      <c r="AZ199">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>7</v>
       </c>
@@ -18564,12 +17769,8 @@
       <c r="AA200" s="1">
         <v>0.23184769316557399</v>
       </c>
-      <c r="AZ200">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>8</v>
       </c>
@@ -18651,12 +17852,8 @@
       <c r="AA201" s="1">
         <v>0.15918020101075309</v>
       </c>
-      <c r="AZ201">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>9</v>
       </c>
@@ -18738,12 +17935,8 @@
       <c r="AA202" s="1">
         <v>0.13313519014660974</v>
       </c>
-      <c r="AZ202">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>10</v>
       </c>
@@ -18825,12 +18018,8 @@
       <c r="AA203" s="1">
         <v>0.22892824212080104</v>
       </c>
-      <c r="AZ203">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>11</v>
       </c>
@@ -18912,12 +18101,8 @@
       <c r="AA204" s="1">
         <v>7.7288570783292224E-2</v>
       </c>
-      <c r="AZ204">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>12</v>
       </c>
@@ -18999,12 +18184,8 @@
       <c r="AA205" s="1">
         <v>0.55794241306146164</v>
       </c>
-      <c r="AZ205">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>13</v>
       </c>
@@ -19086,12 +18267,8 @@
       <c r="AA206" s="1">
         <v>0.81989931552599016</v>
       </c>
-      <c r="AZ206">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14</v>
       </c>
@@ -19173,12 +18350,8 @@
       <c r="AA207" s="1">
         <v>0.55226067057828165</v>
       </c>
-      <c r="AZ207">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>15</v>
       </c>
@@ -19260,12 +18433,8 @@
       <c r="AA208" s="1">
         <v>0.13819579385208627</v>
       </c>
-      <c r="AZ208">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>16</v>
       </c>
@@ -19347,12 +18516,8 @@
       <c r="AA209" s="1">
         <v>0.33597021620982936</v>
       </c>
-      <c r="AZ209">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>17</v>
       </c>
@@ -19434,12 +18599,8 @@
       <c r="AA210" s="1">
         <v>4.6425983364050238E-2</v>
       </c>
-      <c r="AZ210">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>18</v>
       </c>
@@ -19521,12 +18682,8 @@
       <c r="AA211" s="1">
         <v>0.33699094046695777</v>
       </c>
-      <c r="AZ211">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>19</v>
       </c>
@@ -19608,12 +18765,8 @@
       <c r="AA212" s="1">
         <v>0.4733488683159327</v>
       </c>
-      <c r="AZ212">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>20</v>
       </c>
@@ -19695,12 +18848,8 @@
       <c r="AA213" s="1">
         <v>0.25137170943214865</v>
       </c>
-      <c r="AZ213">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>21</v>
       </c>
@@ -19782,12 +18931,8 @@
       <c r="AA214" s="1">
         <v>0.15454388447645931</v>
       </c>
-      <c r="AZ214">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>22</v>
       </c>
@@ -19869,12 +19014,8 @@
       <c r="AA215" s="1">
         <v>0.13176266241313953</v>
       </c>
-      <c r="AZ215">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>23</v>
       </c>
@@ -19956,12 +19097,8 @@
       <c r="AA216" s="1">
         <v>0.22443945305960886</v>
       </c>
-      <c r="AZ216">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>24</v>
       </c>
@@ -20043,12 +19180,8 @@
       <c r="AA217" s="1">
         <v>8.0542826395220313E-2</v>
       </c>
-      <c r="AZ217">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>25</v>
       </c>
@@ -20130,12 +19263,8 @@
       <c r="AA218" s="1">
         <v>0.56341243671892705</v>
       </c>
-      <c r="AZ218">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>26</v>
       </c>
@@ -20217,12 +19346,8 @@
       <c r="AA219" s="1">
         <v>0.75621781529096177</v>
       </c>
-      <c r="AZ219">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>27</v>
       </c>
@@ -20304,12 +19429,8 @@
       <c r="AA220" s="1">
         <v>0.52518906907934626</v>
       </c>
-      <c r="AZ220">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>28</v>
       </c>
@@ -20391,12 +19512,8 @@
       <c r="AA221" s="1">
         <v>0.14226037602420646</v>
       </c>
-      <c r="AZ221">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>29</v>
       </c>
@@ -20478,12 +19595,8 @@
       <c r="AA222" s="1">
         <v>0.30717276910612967</v>
       </c>
-      <c r="AZ222">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>30</v>
       </c>
@@ -20565,12 +19678,8 @@
       <c r="AA223" s="1">
         <v>4.5046993759177457E-2</v>
       </c>
-      <c r="AZ223">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>31</v>
       </c>
@@ -20652,12 +19761,8 @@
       <c r="AA224" s="1">
         <v>0.33044742705983238</v>
       </c>
-      <c r="AZ224">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>32</v>
       </c>
@@ -20739,12 +19844,8 @@
       <c r="AA225" s="1">
         <v>0.46884078385578098</v>
       </c>
-      <c r="AZ225">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>1</v>
       </c>
@@ -20826,12 +19927,8 @@
       <c r="AA226" s="1">
         <v>0.53601770967892048</v>
       </c>
-      <c r="AZ226">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>2</v>
       </c>
@@ -20913,12 +20010,8 @@
       <c r="AA227" s="1">
         <v>0.13006662950784589</v>
       </c>
-      <c r="AZ227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>3</v>
       </c>
@@ -21000,12 +20093,8 @@
       <c r="AA228" s="1">
         <v>0.31037248545098522</v>
       </c>
-      <c r="AZ228">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>4</v>
       </c>
@@ -21087,12 +20176,8 @@
       <c r="AA229" s="1">
         <v>4.5506656960801722E-2</v>
       </c>
-      <c r="AZ229">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>5</v>
       </c>
@@ -21174,12 +20259,8 @@
       <c r="AA230" s="1">
         <v>0.33699094046695777</v>
       </c>
-      <c r="AZ230">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>6</v>
       </c>
@@ -21261,12 +20342,8 @@
       <c r="AA231" s="1">
         <v>0.450808446015174</v>
       </c>
-      <c r="AZ231">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>7</v>
       </c>
@@ -21348,12 +20425,8 @@
       <c r="AA232" s="1">
         <v>0.24405020333218316</v>
       </c>
-      <c r="AZ232">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>8</v>
       </c>
@@ -21435,12 +20508,8 @@
       <c r="AA233" s="1">
         <v>0.15454388447645931</v>
       </c>
-      <c r="AZ233">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>9</v>
       </c>
@@ -21522,12 +20591,8 @@
       <c r="AA234" s="1">
         <v>0.14137035654743096</v>
       </c>
-      <c r="AZ234">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>10</v>
       </c>
@@ -21609,12 +20674,8 @@
       <c r="AA235" s="1">
         <v>0.22892824212080104</v>
       </c>
-      <c r="AZ235">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>11</v>
       </c>
@@ -21696,12 +20757,8 @@
       <c r="AA236" s="1">
         <v>8.0542826395220313E-2</v>
       </c>
-      <c r="AZ236">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>12</v>
       </c>
@@ -21783,12 +20840,8 @@
       <c r="AA237" s="1">
         <v>0.53606231843160046</v>
       </c>
-      <c r="AZ237">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>13</v>
       </c>
@@ -21870,12 +20923,8 @@
       <c r="AA238" s="1">
         <v>0.78009837787909742</v>
       </c>
-      <c r="AZ238">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>14</v>
       </c>
@@ -21957,12 +21006,8 @@
       <c r="AA239" s="1">
         <v>0.52518906907934626</v>
       </c>
-      <c r="AZ239">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>15</v>
       </c>
@@ -22044,12 +21089,8 @@
       <c r="AA240" s="1">
         <v>0.1409055153001664</v>
       </c>
-      <c r="AZ240">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>16</v>
       </c>
@@ -22131,12 +21172,8 @@
       <c r="AA241" s="1">
         <v>0.30397305276127418</v>
       </c>
-      <c r="AZ241">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>17</v>
       </c>
@@ -22218,12 +21255,8 @@
       <c r="AA242" s="1">
         <v>4.5046993759177457E-2</v>
       </c>
-      <c r="AZ242">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>18</v>
       </c>
@@ -22305,12 +21338,8 @@
       <c r="AA243" s="1">
         <v>0.32390391365270693</v>
       </c>
-      <c r="AZ243">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>19</v>
       </c>
@@ -22392,12 +21421,8 @@
       <c r="AA244" s="1">
         <v>0.4282680237144153</v>
       </c>
-      <c r="AZ244">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>20</v>
       </c>
@@ -22479,12 +21504,8 @@
       <c r="AA245" s="1">
         <v>0.23916919926553951</v>
       </c>
-      <c r="AZ245">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>21</v>
       </c>
@@ -22566,12 +21587,8 @@
       <c r="AA246" s="1">
         <v>0.15918020101075309</v>
       </c>
-      <c r="AZ246">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>22</v>
       </c>
@@ -22653,12 +21670,8 @@
       <c r="AA247" s="1">
         <v>0.13999782881396075</v>
       </c>
-      <c r="AZ247">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>23</v>
       </c>
@@ -22740,12 +21753,8 @@
       <c r="AA248" s="1">
         <v>0.2177062694678206</v>
       </c>
-      <c r="AZ248">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>24</v>
       </c>
@@ -22827,12 +21836,8 @@
       <c r="AA249" s="1">
         <v>8.1356390298202338E-2</v>
       </c>
-      <c r="AZ249">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>25</v>
       </c>
@@ -22914,12 +21919,8 @@
       <c r="AA250" s="1">
         <v>0.54700236574653105</v>
       </c>
-      <c r="AZ250">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>26</v>
       </c>
@@ -23001,12 +22002,8 @@
       <c r="AA251" s="1">
         <v>0.79601875293785451</v>
       </c>
-      <c r="AZ251">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>27</v>
       </c>
@@ -23088,12 +22085,8 @@
       <c r="AA252" s="1">
         <v>0.5197747487795592</v>
       </c>
-      <c r="AZ252">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>28</v>
       </c>
@@ -23175,12 +22168,8 @@
       <c r="AA253" s="1">
         <v>0.13006662950784589</v>
       </c>
-      <c r="AZ253">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>29</v>
       </c>
@@ -23262,12 +22251,8 @@
       <c r="AA254" s="1">
         <v>0.31997163448555177</v>
       </c>
-      <c r="AZ254">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>30</v>
       </c>
@@ -23349,12 +22334,8 @@
       <c r="AA255" s="1">
         <v>4.7345309767298761E-2</v>
       </c>
-      <c r="AZ255">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>31</v>
       </c>
@@ -23436,12 +22417,8 @@
       <c r="AA256" s="1">
         <v>0.31736040024558154</v>
       </c>
-      <c r="AZ256">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>32</v>
       </c>
@@ -23523,12 +22500,8 @@
       <c r="AA257" s="1">
         <v>0.4282680237144153</v>
       </c>
-      <c r="AZ257">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>1</v>
       </c>
@@ -23610,12 +22583,8 @@
       <c r="AA258" s="1">
         <v>0.52979124133416533</v>
       </c>
-      <c r="AZ258">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2</v>
       </c>
@@ -23697,12 +22666,8 @@
       <c r="AA259" s="1">
         <v>0.1299988864716439</v>
       </c>
-      <c r="AZ259">
-        <f t="shared" ref="AZ259:AZ322" si="5">$AB259*AA259</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>3</v>
       </c>
@@ -23784,12 +22749,8 @@
       <c r="AA260" s="1">
         <v>0.30701278328888693</v>
       </c>
-      <c r="AZ260">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>4</v>
       </c>
@@ -23871,12 +22832,8 @@
       <c r="AA261" s="1">
         <v>4.1921283988132489E-2</v>
       </c>
-      <c r="AZ261">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>5</v>
       </c>
@@ -23958,12 +22915,8 @@
       <c r="AA262" s="1">
         <v>0.31081688683845615</v>
       </c>
-      <c r="AZ262">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>6</v>
       </c>
@@ -24045,12 +22998,8 @@
       <c r="AA263" s="1">
         <v>0.41970266324012701</v>
       </c>
-      <c r="AZ263">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>7</v>
       </c>
@@ -24132,12 +23081,8 @@
       <c r="AA264" s="1">
         <v>0.23416617009722973</v>
       </c>
-      <c r="AZ264">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>8</v>
       </c>
@@ -24219,12 +23164,8 @@
       <c r="AA265" s="1">
         <v>0.14975302405768906</v>
       </c>
-      <c r="AZ265">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>9</v>
       </c>
@@ -24306,12 +23247,8 @@
       <c r="AA266" s="1">
         <v>0.13169403602646604</v>
       </c>
-      <c r="AZ266">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>10</v>
       </c>
@@ -24393,12 +23330,8 @@
       <c r="AA267" s="1">
         <v>0.20682095599442957</v>
       </c>
-      <c r="AZ267">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>11</v>
       </c>
@@ -24480,12 +23413,8 @@
       <c r="AA268" s="1">
         <v>7.9607227906790992E-2</v>
       </c>
-      <c r="AZ268">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>12</v>
       </c>
@@ -24567,12 +23496,8 @@
       <c r="AA269" s="1">
         <v>0.51965224745920446</v>
       </c>
-      <c r="AZ269">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>13</v>
       </c>
@@ -24654,12 +23579,8 @@
       <c r="AA270" s="1">
         <v>0.76377999344387137</v>
       </c>
-      <c r="AZ270">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>14</v>
       </c>
@@ -24741,12 +23662,8 @@
       <c r="AA271" s="1">
         <v>0.52979124133416533</v>
       </c>
-      <c r="AZ271">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>15</v>
       </c>
@@ -24828,12 +23745,8 @@
       <c r="AA272" s="1">
         <v>0.13257312184732001</v>
       </c>
-      <c r="AZ272">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>16</v>
       </c>
@@ -24915,12 +23828,8 @@
       <c r="AA273" s="1">
         <v>0.30397305276127418</v>
       </c>
-      <c r="AZ273">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>17</v>
       </c>
@@ -25002,12 +23911,8 @@
       <c r="AA274" s="1">
         <v>4.1484603946589441E-2</v>
       </c>
-      <c r="AZ274">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>18</v>
       </c>
@@ -25089,12 +23994,8 @@
       <c r="AA275" s="1">
         <v>0.32324956231199442</v>
       </c>
-      <c r="AZ275">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>19</v>
       </c>
@@ -25176,12 +24077,8 @@
       <c r="AA276" s="1">
         <v>0.44968142490013607</v>
       </c>
-      <c r="AZ276">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>20</v>
       </c>
@@ -25263,12 +24160,8 @@
       <c r="AA277" s="1">
         <v>0.23648464702888547</v>
       </c>
-      <c r="AZ277">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>21</v>
       </c>
@@ -25350,12 +24243,8 @@
       <c r="AA278" s="1">
         <v>0.15122119096021541</v>
       </c>
-      <c r="AZ278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>22</v>
       </c>
@@ -25437,12 +24326,8 @@
       <c r="AA279" s="1">
         <v>0.13169403602646604</v>
       </c>
-      <c r="AZ279">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>23</v>
       </c>
@@ -25524,12 +24409,8 @@
       <c r="AA280" s="1">
         <v>0.21748183001476099</v>
       </c>
-      <c r="AZ280">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>24</v>
       </c>
@@ -25611,12 +24492,8 @@
       <c r="AA281" s="1">
         <v>7.5742799367626373E-2</v>
       </c>
-      <c r="AZ281">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>25</v>
       </c>
@@ -25698,12 +24575,8 @@
       <c r="AA282" s="1">
         <v>0.5300452924083886</v>
       </c>
-      <c r="AZ282">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>26</v>
       </c>
@@ -25785,12 +24658,8 @@
       <c r="AA283" s="1">
         <v>0.77134217159678098</v>
       </c>
-      <c r="AZ283">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>27</v>
       </c>
@@ -25872,12 +24741,8 @@
       <c r="AA284" s="1">
         <v>0.50921682419497438</v>
       </c>
-      <c r="AZ284">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>28</v>
       </c>
@@ -25959,12 +24824,8 @@
       <c r="AA285" s="1">
         <v>0.13386023953515808</v>
       </c>
-      <c r="AZ285">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>29</v>
       </c>
@@ -26046,12 +24907,8 @@
       <c r="AA286" s="1">
         <v>0.29789359170604868</v>
       </c>
-      <c r="AZ286">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>30</v>
       </c>
@@ -26133,12 +24990,8 @@
       <c r="AA287" s="1">
         <v>4.4978044278933815E-2</v>
       </c>
-      <c r="AZ287">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>31</v>
       </c>
@@ -26220,12 +25073,8 @@
       <c r="AA288" s="1">
         <v>0.31392505570684071</v>
       </c>
-      <c r="AZ288">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>32</v>
       </c>
@@ -26307,12 +25156,8 @@
       <c r="AA289" s="1">
         <v>0.40685462252869453</v>
       </c>
-      <c r="AZ289">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>1</v>
       </c>
@@ -26394,12 +25239,8 @@
       <c r="AA290" s="1">
         <v>0.38991367175680802</v>
       </c>
-      <c r="AZ290">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>2</v>
       </c>
@@ -26481,12 +25322,8 @@
       <c r="AA291" s="1">
         <v>0.12626746373434408</v>
       </c>
-      <c r="AZ291">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>3</v>
       </c>
@@ -26568,12 +25405,8 @@
       <c r="AA292" s="1">
         <v>0.29748174575997999</v>
       </c>
-      <c r="AZ292">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>4</v>
       </c>
@@ -26655,12 +25488,8 @@
       <c r="AA293" s="1">
         <v>4.5989104722610467E-2</v>
       </c>
-      <c r="AZ293">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>5</v>
       </c>
@@ -26742,12 +25571,8 @@
       <c r="AA294" s="1">
         <v>0.29758364319182595</v>
       </c>
-      <c r="AZ294">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>6</v>
       </c>
@@ -26829,12 +25654,8 @@
       <c r="AA295" s="1">
         <v>0.46963632109024683</v>
       </c>
-      <c r="AZ295">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>7</v>
       </c>
@@ -26916,12 +25737,8 @@
       <c r="AA296" s="1">
         <v>0.23346439779015135</v>
       </c>
-      <c r="AZ296">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>8</v>
       </c>
@@ -27003,12 +25820,8 @@
       <c r="AA297" s="1">
         <v>0.1479600323897812</v>
       </c>
-      <c r="AZ297">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>9</v>
       </c>
@@ -27090,12 +25903,8 @@
       <c r="AA298" s="1">
         <v>0.14914807358193835</v>
       </c>
-      <c r="AZ298">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>10</v>
       </c>
@@ -27177,12 +25986,8 @@
       <c r="AA299" s="1">
         <v>0.21630483374172366</v>
       </c>
-      <c r="AZ299">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>11</v>
       </c>
@@ -27264,12 +26069,8 @@
       <c r="AA300" s="1">
         <v>7.7467480970060482E-2</v>
       </c>
-      <c r="AZ300">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>12</v>
       </c>
@@ -27351,12 +26152,8 @@
       <c r="AA301" s="1">
         <v>0.42050493603836914</v>
       </c>
-      <c r="AZ301">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>13</v>
       </c>
@@ -27438,12 +26235,8 @@
       <c r="AA302" s="1">
         <v>0.71913619665267769</v>
       </c>
-      <c r="AZ302">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>14</v>
       </c>
@@ -27525,12 +26318,8 @@
       <c r="AA303" s="1">
         <v>0.38462437459764404</v>
       </c>
-      <c r="AZ303">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>15</v>
       </c>
@@ -27612,12 +26401,8 @@
       <c r="AA304" s="1">
         <v>0.11771851435202564</v>
       </c>
-      <c r="AZ304">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>16</v>
       </c>
@@ -27699,12 +26484,8 @@
       <c r="AA305" s="1">
         <v>0.30105279375407817</v>
       </c>
-      <c r="AZ305">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>17</v>
       </c>
@@ -27786,12 +26567,8 @@
       <c r="AA306" s="1">
         <v>4.6766775035971847E-2</v>
       </c>
-      <c r="AZ306">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>18</v>
       </c>
@@ -27873,12 +26650,8 @@
       <c r="AA307" s="1">
         <v>0.30864966612628669</v>
       </c>
-      <c r="AZ307">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>19</v>
       </c>
@@ -27960,12 +26733,8 @@
       <c r="AA308" s="1">
         <v>0.46092865073350575</v>
       </c>
-      <c r="AZ308">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>20</v>
       </c>
@@ -28047,12 +26816,8 @@
       <c r="AA309" s="1">
         <v>0.22107520885198301</v>
       </c>
-      <c r="AZ309">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>21</v>
       </c>
@@ -28134,12 +26899,8 @@
       <c r="AA310" s="1">
         <v>0.14942932593407893</v>
       </c>
-      <c r="AZ310">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>22</v>
       </c>
@@ -28221,12 +26982,8 @@
       <c r="AA311" s="1">
         <v>0.14580624846449972</v>
       </c>
-      <c r="AZ311">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>23</v>
       </c>
@@ -28308,12 +27065,8 @@
       <c r="AA312" s="1">
         <v>0.20833483292938207</v>
       </c>
-      <c r="AZ312">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>24</v>
       </c>
@@ -28395,12 +27148,8 @@
       <c r="AA313" s="1">
         <v>7.6075164377009091E-2</v>
       </c>
-      <c r="AZ313">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>25</v>
       </c>
@@ -28482,12 +27231,8 @@
       <c r="AA314" s="1">
         <v>0.46772855744554459</v>
       </c>
-      <c r="AZ314">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>26</v>
       </c>
@@ -28569,12 +27314,8 @@
       <c r="AA315" s="1">
         <v>0.69763343251953736</v>
       </c>
-      <c r="AZ315">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>27</v>
       </c>
@@ -28656,12 +27397,8 @@
       <c r="AA316" s="1">
         <v>0.38316213563756696</v>
       </c>
-      <c r="AZ316">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>28</v>
       </c>
@@ -28743,12 +27480,8 @@
       <c r="AA317" s="1">
         <v>0.1289304828276106</v>
       </c>
-      <c r="AZ317">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>29</v>
       </c>
@@ -28830,12 +27563,8 @@
       <c r="AA318" s="1">
         <v>0.28713789806851081</v>
       </c>
-      <c r="AZ318">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>30</v>
       </c>
@@ -28917,12 +27646,8 @@
       <c r="AA319" s="1">
         <v>4.4676910970780283E-2</v>
       </c>
-      <c r="AZ319">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>31</v>
       </c>
@@ -29004,12 +27729,8 @@
       <c r="AA320" s="1">
         <v>0.30928644336699423</v>
       </c>
-      <c r="AZ320">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>32</v>
       </c>
@@ -29091,12 +27812,8 @@
       <c r="AA321" s="1">
         <v>0.45203518990861852</v>
       </c>
-      <c r="AZ321">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>1</v>
       </c>
@@ -29178,12 +27895,8 @@
       <c r="AA322" s="1">
         <v>0.37538367038182924</v>
       </c>
-      <c r="AZ322">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>2</v>
       </c>
@@ -29265,12 +27978,8 @@
       <c r="AA323" s="1">
         <v>0.12018811300212001</v>
       </c>
-      <c r="AZ323">
-        <f t="shared" ref="AZ323:AZ385" si="6">$AB323*AA323</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>3</v>
       </c>
@@ -29352,12 +28061,8 @@
       <c r="AA324" s="1">
         <v>0.28154725817896198</v>
       </c>
-      <c r="AZ324">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>4</v>
       </c>
@@ -29439,12 +28144,8 @@
       <c r="AA325" s="1">
         <v>4.6882367854616955E-2</v>
       </c>
-      <c r="AZ325">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>5</v>
       </c>
@@ -29526,12 +28227,8 @@
       <c r="AA326" s="1">
         <v>0.30259669914399334</v>
       </c>
-      <c r="AZ326">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>6</v>
       </c>
@@ -29613,12 +28310,8 @@
       <c r="AA327" s="1">
         <v>0.43565833319397973</v>
       </c>
-      <c r="AZ327">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>7</v>
       </c>
@@ -29700,12 +28393,8 @@
       <c r="AA328" s="1">
         <v>0.21772304768995185</v>
       </c>
-      <c r="AZ328">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>8</v>
       </c>
@@ -29787,12 +28476,8 @@
       <c r="AA329" s="1">
         <v>0.16035307422661751</v>
       </c>
-      <c r="AZ329">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>9</v>
       </c>
@@ -29874,12 +28559,8 @@
       <c r="AA330" s="1">
         <v>0.1386796906061204</v>
       </c>
-      <c r="AZ330">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>10</v>
       </c>
@@ -29961,12 +28642,8 @@
       <c r="AA331" s="1">
         <v>0.2130218266585143</v>
       </c>
-      <c r="AZ331">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>11</v>
       </c>
@@ -30048,12 +28725,8 @@
       <c r="AA332" s="1">
         <v>7.7051441060587519E-2</v>
       </c>
-      <c r="AZ332">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>12</v>
       </c>
@@ -30135,12 +28808,8 @@
       <c r="AA333" s="1">
         <v>0.41695009600600685</v>
       </c>
-      <c r="AZ333">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>13</v>
       </c>
@@ -30222,12 +28891,8 @@
       <c r="AA334" s="1">
         <v>0.71830057796525593</v>
       </c>
-      <c r="AZ334">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14</v>
       </c>
@@ -30309,12 +28974,8 @@
       <c r="AA335" s="1">
         <v>0.35771485362760636</v>
       </c>
-      <c r="AZ335">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>15</v>
       </c>
@@ -30396,12 +29057,8 @@
       <c r="AA336" s="1">
         <v>0.11720366727689044</v>
       </c>
-      <c r="AZ336">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>16</v>
       </c>
@@ -30483,12 +29140,8 @@
       <c r="AA337" s="1">
         <v>0.29742669809320632</v>
       </c>
-      <c r="AZ337">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>17</v>
       </c>
@@ -30570,12 +29223,8 @@
       <c r="AA338" s="1">
         <v>4.3774702556512855E-2</v>
       </c>
-      <c r="AZ338">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>18</v>
       </c>
@@ -30657,12 +29306,8 @@
       <c r="AA339" s="1">
         <v>0.31479827545539374</v>
       </c>
-      <c r="AZ339">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>19</v>
       </c>
@@ -30744,12 +29389,8 @@
       <c r="AA340" s="1">
         <v>0.4436653899862828</v>
       </c>
-      <c r="AZ340">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>20</v>
       </c>
@@ -30831,12 +29472,8 @@
       <c r="AA341" s="1">
         <v>0.23657711677899329</v>
       </c>
-      <c r="AZ341">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>21</v>
       </c>
@@ -30918,12 +29555,8 @@
       <c r="AA342" s="1">
         <v>0.15822983535940957</v>
       </c>
-      <c r="AZ342">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>22</v>
       </c>
@@ -31005,12 +29638,8 @@
       <c r="AA343" s="1">
         <v>0.14485334106993131</v>
       </c>
-      <c r="AZ343">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>23</v>
       </c>
@@ -31092,12 +29721,8 @@
       <c r="AA344" s="1">
         <v>0.20046621042375082</v>
       </c>
-      <c r="AZ344">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>24</v>
       </c>
@@ -31179,12 +29804,8 @@
       <c r="AA345" s="1">
         <v>8.1244140608213222E-2</v>
       </c>
-      <c r="AZ345">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>25</v>
       </c>
@@ -31266,12 +29887,8 @@
       <c r="AA346" s="1">
         <v>0.42038347631675754</v>
       </c>
-      <c r="AZ346">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>26</v>
       </c>
@@ -31353,12 +29970,8 @@
       <c r="AA347" s="1">
         <v>0.76319264462658776</v>
       </c>
-      <c r="AZ347">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>27</v>
       </c>
@@ -31440,12 +30053,8 @@
       <c r="AA348" s="1">
         <v>0.40699492683503591</v>
       </c>
-      <c r="AZ348">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>28</v>
       </c>
@@ -31527,12 +30136,8 @@
       <c r="AA349" s="1">
         <v>0.12384606230212507</v>
       </c>
-      <c r="AZ349">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>29</v>
       </c>
@@ -31614,12 +30219,8 @@
       <c r="AA350" s="1">
         <v>0.29237113682890775</v>
       </c>
-      <c r="AZ350">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>30</v>
       </c>
@@ -31701,12 +30302,8 @@
       <c r="AA351" s="1">
         <v>5.043452388991345E-2</v>
       </c>
-      <c r="AZ351">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>31</v>
       </c>
@@ -31788,12 +30385,8 @@
       <c r="AA352" s="1">
         <v>0.33298126403136252</v>
       </c>
-      <c r="AZ352">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>32</v>
       </c>
@@ -31875,12 +30468,8 @@
       <c r="AA353" s="1">
         <v>0.43966360856781511</v>
       </c>
-      <c r="AZ353">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>1</v>
       </c>
@@ -31962,12 +30551,8 @@
       <c r="AA354" s="1">
         <v>0.36542259844303537</v>
       </c>
-      <c r="AZ354">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>2</v>
       </c>
@@ -32049,12 +30634,8 @@
       <c r="AA355" s="1">
         <v>0.11993956495672245</v>
       </c>
-      <c r="AZ355">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>3</v>
       </c>
@@ -32136,12 +30717,8 @@
       <c r="AA356" s="1">
         <v>0.29133395395230999</v>
       </c>
-      <c r="AZ356">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>4</v>
       </c>
@@ -32223,12 +30800,8 @@
       <c r="AA357" s="1">
         <v>4.6491627052506763E-2</v>
       </c>
-      <c r="AZ357">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>5</v>
       </c>
@@ -32310,12 +30883,8 @@
       <c r="AA358" s="1">
         <v>0.33094444964029684</v>
       </c>
-      <c r="AZ358">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>6</v>
       </c>
@@ -32397,12 +30966,8 @@
       <c r="AA359" s="1">
         <v>0.44131775373106019</v>
       </c>
-      <c r="AZ359">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>7</v>
       </c>
@@ -32484,12 +31049,8 @@
       <c r="AA360" s="1">
         <v>0.21940458410267669</v>
       </c>
-      <c r="AZ360">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>8</v>
       </c>
@@ -32571,12 +31132,8 @@
       <c r="AA361" s="1">
         <v>0.14882351390693122</v>
       </c>
-      <c r="AZ361">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>9</v>
       </c>
@@ -32658,12 +31215,8 @@
       <c r="AA362" s="1">
         <v>0.14232419957901937</v>
       </c>
-      <c r="AZ362">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>10</v>
       </c>
@@ -32745,12 +31298,8 @@
       <c r="AA363" s="1">
         <v>0.1987066051117635</v>
       </c>
-      <c r="AZ363">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>11</v>
       </c>
@@ -32832,12 +31381,8 @@
       <c r="AA364" s="1">
         <v>8.2968124911176055E-2</v>
       </c>
-      <c r="AZ364">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>12</v>
       </c>
@@ -32919,12 +31464,8 @@
       <c r="AA365" s="1">
         <v>0.44534195487828471</v>
       </c>
-      <c r="AZ365">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>13</v>
       </c>
@@ -33006,12 +31547,8 @@
       <c r="AA366" s="1">
         <v>0.72046342351678183</v>
       </c>
-      <c r="AZ366">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14</v>
       </c>
@@ -33093,12 +31630,8 @@
       <c r="AA367" s="1">
         <v>0.3905046989223474</v>
       </c>
-      <c r="AZ367">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>15</v>
       </c>
@@ -33180,12 +31713,8 @@
       <c r="AA368" s="1">
         <v>0.12557691115573524</v>
       </c>
-      <c r="AZ368">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>16</v>
       </c>
@@ -33267,12 +31796,8 @@
       <c r="AA369" s="1">
         <v>0.29689256902968525</v>
       </c>
-      <c r="AZ369">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>17</v>
       </c>
@@ -33354,12 +31879,8 @@
       <c r="AA370" s="1">
         <v>4.5766371175294397E-2</v>
       </c>
-      <c r="AZ370">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>18</v>
       </c>
@@ -33441,12 +31962,8 @@
       <c r="AA371" s="1">
         <v>0.32149215231149958</v>
       </c>
-      <c r="AZ371">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>19</v>
       </c>
@@ -33528,12 +32045,8 @@
       <c r="AA372" s="1">
         <v>0.43026063286055011</v>
       </c>
-      <c r="AZ372">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>20</v>
       </c>
@@ -33615,12 +32128,8 @@
       <c r="AA373" s="1">
         <v>0.21739521351587132</v>
       </c>
-      <c r="AZ373">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>21</v>
       </c>
@@ -33702,12 +32211,8 @@
       <c r="AA374" s="1">
         <v>0.14757998683067833</v>
       </c>
-      <c r="AZ374">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>22</v>
       </c>
@@ -33789,12 +32294,8 @@
       <c r="AA375" s="1">
         <v>0.13246396666318053</v>
       </c>
-      <c r="AZ375">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>23</v>
       </c>
@@ -33876,12 +32377,8 @@
       <c r="AA376" s="1">
         <v>0.19190004695921983</v>
       </c>
-      <c r="AZ376">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>24</v>
       </c>
@@ -33963,12 +32460,8 @@
       <c r="AA377" s="1">
         <v>8.0102468745015948E-2</v>
       </c>
-      <c r="AZ377">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>25</v>
       </c>
@@ -34050,12 +32543,8 @@
       <c r="AA378" s="1">
         <v>0.41896012228240564</v>
       </c>
-      <c r="AZ378">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>26</v>
       </c>
@@ -34137,12 +32626,8 @@
       <c r="AA379" s="1">
         <v>0.68614524604916194</v>
       </c>
-      <c r="AZ379">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>27</v>
       </c>
@@ -34224,12 +32709,8 @@
       <c r="AA380" s="1">
         <v>0.38248935213953739</v>
       </c>
-      <c r="AZ380">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>28</v>
       </c>
@@ -34311,12 +32792,8 @@
       <c r="AA381" s="1">
         <v>0.12614241732230266</v>
       </c>
-      <c r="AZ381">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>29</v>
       </c>
@@ -34398,12 +32875,8 @@
       <c r="AA382" s="1">
         <v>0.30007397257087931</v>
       </c>
-      <c r="AZ382">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>30</v>
       </c>
@@ -34485,12 +32958,8 @@
       <c r="AA383" s="1">
         <v>4.6078634270013533E-2</v>
       </c>
-      <c r="AZ383">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>31</v>
       </c>
@@ -34571,10 +33040,6 @@
       </c>
       <c r="AA384" s="1">
         <v>0.29177639938549099</v>
-      </c>
-      <c r="AZ384">
-        <f t="shared" si="6"/>
-        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:27" x14ac:dyDescent="0.3">

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF94B4E-1449-4897-B761-D3B45613BFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BF1AD7-FFA8-4ECA-9F99-53B30C515317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38010" yWindow="-12540" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BF1AD7-FFA8-4ECA-9F99-53B30C515317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BC551E-CC7F-244D-969E-3FD8615CF118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38010" yWindow="-12540" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -442,13 +442,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -468,7 +468,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -476,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -488,7 +488,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -496,7 +496,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -508,7 +508,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -516,7 +516,7 @@
         <v>4.8</v>
       </c>
       <c r="C4" s="1">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -528,7 +528,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -536,7 +536,7 @@
         <v>2.4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -548,7 +548,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -556,7 +556,7 @@
         <v>2.4</v>
       </c>
       <c r="C6" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -568,7 +568,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -576,7 +576,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -588,7 +588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -596,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -608,7 +608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -616,7 +616,7 @@
         <v>2.4</v>
       </c>
       <c r="C9" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -628,7 +628,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -636,7 +636,7 @@
         <v>2.4</v>
       </c>
       <c r="C10" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -648,7 +648,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -656,7 +656,7 @@
         <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -668,7 +668,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -676,7 +676,7 @@
         <v>2.4</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6800000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -688,7 +688,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -696,7 +696,7 @@
         <v>2.4</v>
       </c>
       <c r="C13" s="1">
-        <v>1.6800000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -708,7 +708,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -716,7 +716,7 @@
         <v>4.8</v>
       </c>
       <c r="C14" s="1">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -728,7 +728,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -736,7 +736,7 @@
         <v>2.4</v>
       </c>
       <c r="C15" s="1">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -748,7 +748,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -756,7 +756,7 @@
         <v>2.4</v>
       </c>
       <c r="C16" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -768,7 +768,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -776,7 +776,7 @@
         <v>2.4</v>
       </c>
       <c r="C17" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -788,7 +788,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -796,7 +796,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -808,7 +808,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -816,7 +816,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -828,7 +828,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -836,7 +836,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,7 +848,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -856,7 +856,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -868,7 +868,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -876,7 +876,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -888,7 +888,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -896,7 +896,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -908,7 +908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>16.8</v>
       </c>
       <c r="C24" s="1">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -928,7 +928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16.8</v>
       </c>
       <c r="C25" s="1">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -948,7 +948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -956,7 +956,7 @@
         <v>2.4</v>
       </c>
       <c r="C26" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -968,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -976,7 +976,7 @@
         <v>2.4</v>
       </c>
       <c r="C27" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -996,7 +996,7 @@
         <v>2.4</v>
       </c>
       <c r="C28" s="1">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1008,7 +1008,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>4.8</v>
       </c>
       <c r="C29" s="1">
-        <v>3.3600000000000003</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1028,7 +1028,7 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1048,7 +1048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>3.3600000000000003</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1068,7 +1068,7 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>8.4</v>
       </c>
       <c r="C32" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1088,7 +1088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>2.4</v>
       </c>
       <c r="C33" s="1">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1108,11 +1108,11 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
@@ -1125,12 +1125,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD68AE75-D6B1-4AA7-B0E5-5751542FB30D}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1154,10 +1154,10 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
   </sheetData>
@@ -1168,9 +1168,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206E5596-3B52-412C-A9A4-71C002FACF4D}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>0.30423493001908397</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>0.12215315627057644</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>5.140697371227413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>0.31988431141736134</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>0.45601221277188941</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0.23212504519623703</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>0.16447266993333343</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0.14884669085844837</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0.21182466623223417</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>8.8097283050149661E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>0.37751283536620156</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0.71253728546098483</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0.1208807275594246</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>0.29717043793976544</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>5.090787688011613E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>0.47011568326998909</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0.22743565034378779</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>0.16275941295486118</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0.15970009540021024</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>0.21390137864627567</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>8.3063152590141104E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>0.38918849006824902</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>0.764493129192515</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>0.31025938407886783</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>0.12724287111518379</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>5.240516737659013E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>0.47951799693538888</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>0.3164043272198474</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>0.13497923767898695</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>0.32167183731275839</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>5.1387009838987807E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>0.33607437452583194</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>0.25360247362045452</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>0.17105157673066676</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>0.15480055849278632</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>0.20949874832850765</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>9.1621174372155653E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>0.40070846937426924</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>0.7796345465085609</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>0.32266975944202259</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>0.12968593424059532</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>0.31851819184890778</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -5320,7 +5320,7 @@
         <v>4.9310767017210523E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0.35644251843648839</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>0.51336632613082811</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>0.23653307635753931</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>0.17283336398827787</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>0.16286308758095228</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>0.213818310149714</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>8.2895348241474168E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>0.40880358996768879</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>0.81051116221187025</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>0.3070061788865846</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>0.12703928252139948</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>0.30905725545735607</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>5.0867949133543484E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>0.32589030257050366</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>0.47425270128276498</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>0.28043833648293781</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>0.12594499382980892</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>0.30014214231916309</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>5.1357064029058326E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>0.22518474081461215</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>0.1729361594069862</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>0.14435028040543274</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>0.2035178165760681</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>0.38903281467222173</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>0.70556035787417926</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>0.29224626644011414</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>0.13093291437752413</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>0.29122702918097015</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>5.0378834238028643E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>0.33587852698822945</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>0.4422848348204057</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>0.22748254429231229</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>0.17629414308479177</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>0.14890871031297273</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>0.20555299474182878</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>0.38521876746955291</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>0.72010799411900772</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>0.1184631130082361</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>0.30311384669856073</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>4.9889719342513801E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>0.40460512983649527</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>0.12531670023913216</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>0.29869072399109714</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>4.4140186966755215E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>0.31506655879445489</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>0.44456052640476812</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>0.24397437503436967</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>0.15382663214631914</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>0.14269317780774657</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>0.21685736810291287</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>7.9818120109252197E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>0.45025918839909279</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>0.78440506467065618</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>0.4349917738149664</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -10466,7 +10466,7 @@
         <v>0.12151477012193317</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>0.29988121067334794</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>4.4687934013653223E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -10715,7 +10715,7 @@
         <v>0.33018527981719359</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>0.42311155071818235</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>0.23439270222739572</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -10964,7 +10964,7 @@
         <v>0.15708373083840152</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>0.14033793264830885</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>0.19882125121158906</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>7.9720383742063805E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>0.42271478599915069</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>0.7719433123864361</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>0.42260815392379569</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>0.12503041680988139</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>0.30983513447948846</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -11711,7 +11711,7 @@
         <v>4.7369169177349381E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>0.29376889231153613</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>0.40276293406267627</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>0.42689047219041887</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>0.12033783871790973</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -12126,7 +12126,7 @@
         <v>0.29665445719231714</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12209,7 +12209,7 @@
         <v>4.2953112347665981E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>0.3215536643614364</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>0.44732388733607209</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>0.21766051836345818</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>0.13917647670381256</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>0.13581314695342595</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -12707,7 +12707,7 @@
         <v>0.18744030886223878</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>7.5711443802736714E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>0.45877795420658402</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -12956,7 +12956,7 @@
         <v>0.72691636268398796</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>0.40804281413635179</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>0.11968020682142257</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>0.2817710283800931</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>4.7180765681348061E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>0.3246823184506501</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -13454,7 +13454,7 @@
         <v>0.4378654235287498</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>0.2315525622208352</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>0.15065394992841988</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>0.13333519255883414</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>0.2201848013021738</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>7.5208128585683348E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>0.42885448722957481</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>0.75957708235256871</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>0.41003335984872546</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -14201,7 +14201,7 @@
         <v>0.12746094767742908</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>0.31004400592124742</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>4.6176909736852456E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>0.31071405402795677</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -14533,7 +14533,7 @@
         <v>0.44091942255282457</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>0.42965036203221812</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>0.12289737753343244</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>0.28273252588643172</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>4.083949069934821E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>0.32221764217060544</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>0.46171304926561546</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>0.24146630603376001</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>0.16428246479929443</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -15280,7 +15280,7 @@
         <v>0.13144036344599996</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>0.19702677154429635</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>7.2314319481827663E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -15529,7 +15529,7 @@
         <v>0.46001998724932369</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -15612,7 +15612,7 @@
         <v>0.72622447296762938</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>0.4010627508493424</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>0.12537432575955593</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>0.31273459745725996</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -15944,7 +15944,7 @@
         <v>4.4051037967967832E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>0.29278258429582177</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>0.43040774612253258</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>0.22549174696111235</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>0.14289138994230252</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>0.13544434056330421</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>0.21582499841669786</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -16525,7 +16525,7 @@
         <v>8.3930712813533967E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>0.45973303128551724</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -16691,7 +16691,7 @@
         <v>0.73190418906602639</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>0.39427768777634509</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>0.12672797661677199</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -16940,7 +16940,7 @@
         <v>0.29363456677379773</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -17023,7 +17023,7 @@
         <v>4.8685903486685111E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>0.31338468480191034</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>0.45918880408260448</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>0.56850363147764293</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -17355,7 +17355,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>4.6885646565674503E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>0.32717567035626965</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -17687,7 +17687,7 @@
         <v>0.45982461493547749</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -17770,7 +17770,7 @@
         <v>0.23184769316557399</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -17853,7 +17853,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -17936,7 +17936,7 @@
         <v>0.13313519014660974</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -18102,7 +18102,7 @@
         <v>7.7288570783292224E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -18185,7 +18185,7 @@
         <v>0.55794241306146164</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -18268,7 +18268,7 @@
         <v>0.81989931552599016</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -18351,7 +18351,7 @@
         <v>0.55226067057828165</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -18434,7 +18434,7 @@
         <v>0.13819579385208627</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -18517,7 +18517,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>4.6425983364050238E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -18683,7 +18683,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>0.4733488683159327</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>0.25137170943214865</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -18932,7 +18932,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -19015,7 +19015,7 @@
         <v>0.13176266241313953</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>0.22443945305960886</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -19181,7 +19181,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>0.56341243671892705</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -19347,7 +19347,7 @@
         <v>0.75621781529096177</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -19430,7 +19430,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>0.14226037602420646</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -19596,7 +19596,7 @@
         <v>0.30717276910612967</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -19762,7 +19762,7 @@
         <v>0.33044742705983238</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>0.46884078385578098</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -19928,7 +19928,7 @@
         <v>0.53601770967892048</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -20011,7 +20011,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>0.31037248545098522</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -20177,7 +20177,7 @@
         <v>4.5506656960801722E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>0.450808446015174</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -20426,7 +20426,7 @@
         <v>0.24405020333218316</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -20509,7 +20509,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>0.14137035654743096</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>0.53606231843160046</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -20924,7 +20924,7 @@
         <v>0.78009837787909742</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -21007,7 +21007,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -21173,7 +21173,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -21256,7 +21256,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -21339,7 +21339,7 @@
         <v>0.32390391365270693</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -21422,7 +21422,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -21505,7 +21505,7 @@
         <v>0.23916919926553951</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -21588,7 +21588,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -21671,7 +21671,7 @@
         <v>0.13999782881396075</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>0.2177062694678206</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -21837,7 +21837,7 @@
         <v>8.1356390298202338E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>0.54700236574653105</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -22003,7 +22003,7 @@
         <v>0.79601875293785451</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -22086,7 +22086,7 @@
         <v>0.5197747487795592</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -22169,7 +22169,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -22252,7 +22252,7 @@
         <v>0.31997163448555177</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -22335,7 +22335,7 @@
         <v>4.7345309767298761E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>0.31736040024558154</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -22501,7 +22501,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>0.1299988864716439</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -22750,7 +22750,7 @@
         <v>0.30701278328888693</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>4.1921283988132489E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -22916,7 +22916,7 @@
         <v>0.31081688683845615</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -22999,7 +22999,7 @@
         <v>0.41970266324012701</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -23082,7 +23082,7 @@
         <v>0.23416617009722973</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -23165,7 +23165,7 @@
         <v>0.14975302405768906</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -23248,7 +23248,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -23331,7 +23331,7 @@
         <v>0.20682095599442957</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -23414,7 +23414,7 @@
         <v>7.9607227906790992E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -23497,7 +23497,7 @@
         <v>0.51965224745920446</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -23580,7 +23580,7 @@
         <v>0.76377999344387137</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -23663,7 +23663,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -23746,7 +23746,7 @@
         <v>0.13257312184732001</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -23829,7 +23829,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>4.1484603946589441E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -23995,7 +23995,7 @@
         <v>0.32324956231199442</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -24078,7 +24078,7 @@
         <v>0.44968142490013607</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -24161,7 +24161,7 @@
         <v>0.23648464702888547</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -24244,7 +24244,7 @@
         <v>0.15122119096021541</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -24327,7 +24327,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -24410,7 +24410,7 @@
         <v>0.21748183001476099</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -24493,7 +24493,7 @@
         <v>7.5742799367626373E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -24576,7 +24576,7 @@
         <v>0.5300452924083886</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -24659,7 +24659,7 @@
         <v>0.77134217159678098</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>0.50921682419497438</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -24825,7 +24825,7 @@
         <v>0.13386023953515808</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -24908,7 +24908,7 @@
         <v>0.29789359170604868</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>4.4978044278933815E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -25074,7 +25074,7 @@
         <v>0.31392505570684071</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -25157,7 +25157,7 @@
         <v>0.40685462252869453</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -25240,7 +25240,7 @@
         <v>0.38991367175680802</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -25323,7 +25323,7 @@
         <v>0.12626746373434408</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -25406,7 +25406,7 @@
         <v>0.29748174575997999</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -25489,7 +25489,7 @@
         <v>4.5989104722610467E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -25572,7 +25572,7 @@
         <v>0.29758364319182595</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -25655,7 +25655,7 @@
         <v>0.46963632109024683</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -25738,7 +25738,7 @@
         <v>0.23346439779015135</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -25821,7 +25821,7 @@
         <v>0.1479600323897812</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -25904,7 +25904,7 @@
         <v>0.14914807358193835</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -25987,7 +25987,7 @@
         <v>0.21630483374172366</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -26070,7 +26070,7 @@
         <v>7.7467480970060482E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -26153,7 +26153,7 @@
         <v>0.42050493603836914</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -26236,7 +26236,7 @@
         <v>0.71913619665267769</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -26319,7 +26319,7 @@
         <v>0.38462437459764404</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -26402,7 +26402,7 @@
         <v>0.11771851435202564</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -26485,7 +26485,7 @@
         <v>0.30105279375407817</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -26568,7 +26568,7 @@
         <v>4.6766775035971847E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -26651,7 +26651,7 @@
         <v>0.30864966612628669</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -26734,7 +26734,7 @@
         <v>0.46092865073350575</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -26817,7 +26817,7 @@
         <v>0.22107520885198301</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>0.14942932593407893</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -26983,7 +26983,7 @@
         <v>0.14580624846449972</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -27066,7 +27066,7 @@
         <v>0.20833483292938207</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -27149,7 +27149,7 @@
         <v>7.6075164377009091E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -27232,7 +27232,7 @@
         <v>0.46772855744554459</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -27315,7 +27315,7 @@
         <v>0.69763343251953736</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -27398,7 +27398,7 @@
         <v>0.38316213563756696</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -27481,7 +27481,7 @@
         <v>0.1289304828276106</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -27564,7 +27564,7 @@
         <v>0.28713789806851081</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -27647,7 +27647,7 @@
         <v>4.4676910970780283E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -27730,7 +27730,7 @@
         <v>0.30928644336699423</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -27813,7 +27813,7 @@
         <v>0.45203518990861852</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -27896,7 +27896,7 @@
         <v>0.37538367038182924</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -27979,7 +27979,7 @@
         <v>0.12018811300212001</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -28062,7 +28062,7 @@
         <v>0.28154725817896198</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -28145,7 +28145,7 @@
         <v>4.6882367854616955E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -28228,7 +28228,7 @@
         <v>0.30259669914399334</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -28311,7 +28311,7 @@
         <v>0.43565833319397973</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -28394,7 +28394,7 @@
         <v>0.21772304768995185</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -28477,7 +28477,7 @@
         <v>0.16035307422661751</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -28560,7 +28560,7 @@
         <v>0.1386796906061204</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -28643,7 +28643,7 @@
         <v>0.2130218266585143</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -28726,7 +28726,7 @@
         <v>7.7051441060587519E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -28809,7 +28809,7 @@
         <v>0.41695009600600685</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>0.71830057796525593</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -28975,7 +28975,7 @@
         <v>0.35771485362760636</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -29058,7 +29058,7 @@
         <v>0.11720366727689044</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -29141,7 +29141,7 @@
         <v>0.29742669809320632</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -29224,7 +29224,7 @@
         <v>4.3774702556512855E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -29307,7 +29307,7 @@
         <v>0.31479827545539374</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -29390,7 +29390,7 @@
         <v>0.4436653899862828</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>0.23657711677899329</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -29556,7 +29556,7 @@
         <v>0.15822983535940957</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -29639,7 +29639,7 @@
         <v>0.14485334106993131</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -29722,7 +29722,7 @@
         <v>0.20046621042375082</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -29805,7 +29805,7 @@
         <v>8.1244140608213222E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -29888,7 +29888,7 @@
         <v>0.42038347631675754</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>0.76319264462658776</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -30054,7 +30054,7 @@
         <v>0.40699492683503591</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -30137,7 +30137,7 @@
         <v>0.12384606230212507</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -30220,7 +30220,7 @@
         <v>0.29237113682890775</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -30303,7 +30303,7 @@
         <v>5.043452388991345E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -30386,7 +30386,7 @@
         <v>0.33298126403136252</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -30469,7 +30469,7 @@
         <v>0.43966360856781511</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -30552,7 +30552,7 @@
         <v>0.36542259844303537</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -30635,7 +30635,7 @@
         <v>0.11993956495672245</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -30718,7 +30718,7 @@
         <v>0.29133395395230999</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -30801,7 +30801,7 @@
         <v>4.6491627052506763E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -30884,7 +30884,7 @@
         <v>0.33094444964029684</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -30967,7 +30967,7 @@
         <v>0.44131775373106019</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -31050,7 +31050,7 @@
         <v>0.21940458410267669</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -31133,7 +31133,7 @@
         <v>0.14882351390693122</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -31216,7 +31216,7 @@
         <v>0.14232419957901937</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -31299,7 +31299,7 @@
         <v>0.1987066051117635</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -31382,7 +31382,7 @@
         <v>8.2968124911176055E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -31465,7 +31465,7 @@
         <v>0.44534195487828471</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -31548,7 +31548,7 @@
         <v>0.72046342351678183</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -31631,7 +31631,7 @@
         <v>0.3905046989223474</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -31714,7 +31714,7 @@
         <v>0.12557691115573524</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -31797,7 +31797,7 @@
         <v>0.29689256902968525</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -31880,7 +31880,7 @@
         <v>4.5766371175294397E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -31963,7 +31963,7 @@
         <v>0.32149215231149958</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -32046,7 +32046,7 @@
         <v>0.43026063286055011</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -32129,7 +32129,7 @@
         <v>0.21739521351587132</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -32212,7 +32212,7 @@
         <v>0.14757998683067833</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -32295,7 +32295,7 @@
         <v>0.13246396666318053</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -32378,7 +32378,7 @@
         <v>0.19190004695921983</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -32461,7 +32461,7 @@
         <v>8.0102468745015948E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -32544,7 +32544,7 @@
         <v>0.41896012228240564</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -32627,7 +32627,7 @@
         <v>0.68614524604916194</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -32710,7 +32710,7 @@
         <v>0.38248935213953739</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -32793,7 +32793,7 @@
         <v>0.12614241732230266</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -32876,7 +32876,7 @@
         <v>0.30007397257087931</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -32959,7 +32959,7 @@
         <v>4.6078634270013533E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -33042,7 +33042,7 @@
         <v>0.29177639938549099</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -33133,9 +33133,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB35780-D2A8-4868-BC60-ED161DD3DC9F}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -33218,7 +33218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -33301,7 +33301,7 @@
         <v>0.10440066304416196</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -33384,7 +33384,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -33467,7 +33467,7 @@
         <v>-0.28973750613877669</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -33550,7 +33550,7 @@
         <v>-0.29715603926547057</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -33633,7 +33633,7 @@
         <v>-0.25022140873816789</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -33716,7 +33716,7 @@
         <v>0.22534376338021103</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -33799,7 +33799,7 @@
         <v>-0.22749198791228348</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -33882,7 +33882,7 @@
         <v>-0.72083640057428056</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -33965,7 +33965,7 @@
         <v>-2.726202685746134E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -34048,7 +34048,7 @@
         <v>-0.28544317332426927</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -34131,7 +34131,7 @@
         <v>-0.17665658184026775</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -34214,7 +34214,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -34297,7 +34297,7 @@
         <v>0.16425412952137319</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -34380,7 +34380,7 @@
         <v>0.10239295798562037</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -34463,7 +34463,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -34546,7 +34546,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -34629,7 +34629,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -34712,7 +34712,7 @@
         <v>-0.26827862380174705</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -34795,7 +34795,7 @@
         <v>0.2392825528676468</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -34878,7 +34878,7 @@
         <v>-0.21882562646800599</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -34961,7 +34961,7 @@
         <v>-0.75118740691425023</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -35044,7 +35044,7 @@
         <v>-2.4902812994796415E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -35127,7 +35127,7 @@
         <v>-0.30309945208659528</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -35210,7 +35210,7 @@
         <v>-0.17308776200511083</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -35293,7 +35293,7 @@
         <v>0.27925369820311069</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -35376,7 +35376,7 @@
         <v>0.16267476289135999</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -35459,7 +35459,7 @@
         <v>9.9381400397808003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -35542,7 +35542,7 @@
         <v>-0.10003293563076388</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -35625,7 +35625,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -35708,7 +35708,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -35791,7 +35791,7 @@
         <v>-0.25796021519398754</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -35874,7 +35874,7 @@
         <v>0.2346362897051682</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -35957,7 +35957,7 @@
         <v>0.10546474672518899</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -36040,7 +36040,7 @@
         <v>-9.9942905988696193E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -36123,7 +36123,7 @@
         <v>-0.2842186964980381</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -36206,7 +36206,7 @@
         <v>-0.3060707204434347</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -36289,7 +36289,7 @@
         <v>-0.26569902164980719</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>0.24646102945367621</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -36455,7 +36455,7 @@
         <v>-0.21869563104634182</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -36538,7 +36538,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -36621,7 +36621,7 @@
         <v>-2.5919896304478624E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -36704,7 +36704,7 @@
         <v>-0.30916144112832716</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -36787,7 +36787,7 @@
         <v>-0.18747010594079325</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -36870,7 +36870,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -36953,7 +36953,7 @@
         <v>0.15454102474679199</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -37036,7 +37036,7 @@
         <v>0.10753268293548682</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -37119,7 +37119,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -37202,7 +37202,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -37285,7 +37285,7 @@
         <v>-0.31895790867263196</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -37368,7 +37368,7 @@
         <v>-0.26038504121681105</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -37451,7 +37451,7 @@
         <v>0.22731842522426446</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -37534,7 +37534,7 @@
         <v>-0.22762198333394762</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -37617,7 +37617,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -37700,7 +37700,7 @@
         <v>-2.7539889823508541E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -37783,7 +37783,7 @@
         <v>-0.29703746304486339</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -37866,7 +37866,7 @@
         <v>-0.17644245265015834</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -37949,7 +37949,7 @@
         <v>0.27891520887195537</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -38032,7 +38032,7 @@
         <v>0.16592825814918719</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -38115,7 +38115,7 @@
         <v>0.10029490619944442</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -38198,7 +38198,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -38281,7 +38281,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -38364,7 +38364,7 @@
         <v>-0.32217970572993126</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -38447,7 +38447,7 @@
         <v>-0.25772805100031299</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -38530,7 +38530,7 @@
         <v>0.23210407628161739</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -38613,7 +38613,7 @@
         <v>0.10329642526196409</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -38696,7 +38696,7 @@
         <v>-9.9012599687330088E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -38779,7 +38779,7 @@
         <v>-0.26230902222430585</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -38862,7 +38862,7 @@
         <v>-0.30347451504774686</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -38945,7 +38945,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -39028,7 +39028,7 @@
         <v>0.23677357075990837</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -39111,7 +39111,7 @@
         <v>-0.21869563104634185</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -39194,7 +39194,7 @@
         <v>-0.75847164843584303</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -39277,7 +39277,7 @@
         <v>-2.5175433263371027E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -39360,7 +39360,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -39443,7 +39443,7 @@
         <v>-0.17662089364191619</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -39526,7 +39526,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -39609,7 +39609,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -39692,7 +39692,7 @@
         <v>9.7393772389851849E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -39775,7 +39775,7 @@
         <v>-0.10195356799487455</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -39858,7 +39858,7 @@
         <v>-0.27853432256807731</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -39941,7 +39941,7 @@
         <v>-0.30960531333153979</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -40024,7 +40024,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -40107,7 +40107,7 @@
         <v>0.23222023286067936</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -40190,7 +40190,7 @@
         <v>-0.21444911393864588</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -40273,7 +40273,7 @@
         <v>-0.72872766222267271</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -40356,7 +40356,7 @@
         <v>-2.5689217615684722E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -40439,7 +40439,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -40522,7 +40522,7 @@
         <v>-0.17137472848423552</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -40605,7 +40605,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -40688,7 +40688,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -40771,7 +40771,7 @@
         <v>0.10231264978327871</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -40854,7 +40854,7 @@
         <v>-9.6071631379785624E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -40937,7 +40937,7 @@
         <v>-0.27042167239619158</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -41020,7 +41020,7 @@
         <v>-0.31573611161533266</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -41103,7 +41103,7 @@
         <v>-0.25785703110790992</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -41186,7 +41186,7 @@
         <v>0.22311355706222133</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -41269,7 +41269,7 @@
         <v>0.23760749463551797</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -41352,7 +41352,7 @@
         <v>-3.5905771033493038E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -41435,7 +41435,7 @@
         <v>-0.20578658689322218</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -41518,7 +41518,7 @@
         <v>-0.28962811170780051</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -41601,7 +41601,7 @@
         <v>-0.12389553246065828</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -41684,7 +41684,7 @@
         <v>0.33237688508273816</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -41767,7 +41767,7 @@
         <v>-0.15590387379103984</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -41850,7 +41850,7 @@
         <v>-0.828655542709546</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -41933,7 +41933,7 @@
         <v>-1.6089547589897894E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -42016,7 +42016,7 @@
         <v>-0.15731781796771568</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -42099,7 +42099,7 @@
         <v>-0.13524649072189965</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -42182,7 +42182,7 @@
         <v>0.38975295617822353</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -42265,7 +42265,7 @@
         <v>0.18031544078576742</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -42348,7 +42348,7 @@
         <v>0.22202818712711603</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -42431,7 +42431,7 @@
         <v>-3.5986237224313211E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -42514,7 +42514,7 @@
         <v>-0.19719024690254594</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -42597,7 +42597,7 @@
         <v>-0.26353988069316525</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -42680,7 +42680,7 @@
         <v>-0.114817589943775</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -42763,7 +42763,7 @@
         <v>0.34470553774825213</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -42846,7 +42846,7 @@
         <v>-0.16614510917506134</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -42929,7 +42929,7 @@
         <v>-0.75903892741456302</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -43012,7 +43012,7 @@
         <v>-1.4912564087038236E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -43095,7 +43095,7 @@
         <v>-0.17396207697380037</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -43178,7 +43178,7 @@
         <v>-0.13971909935658441</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -43261,7 +43261,7 @@
         <v>0.40211757717383378</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -43344,7 +43344,7 @@
         <v>0.18313533440208066</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -43427,7 +43427,7 @@
         <v>0.22566608737329294</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -43510,7 +43510,7 @@
         <v>-3.7456848986658464E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -43593,7 +43593,7 @@
         <v>-0.21267994555977024</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -43676,7 +43676,7 @@
         <v>-0.2674527790746834</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -43759,7 +43759,7 @@
         <v>-0.11245437744379867</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -43842,7 +43842,7 @@
         <v>0.3109013348788397</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -43925,7 +43925,7 @@
         <v>0.2307535183084562</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -44008,7 +44008,7 @@
         <v>-3.531095206826363E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -44091,7 +44091,7 @@
         <v>-0.2146930384344056</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -44174,7 +44174,7 @@
         <v>-0.2546406723509716</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -44257,7 +44257,7 @@
         <v>-0.12220395679471781</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -44340,7 +44340,7 @@
         <v>0.30166028657189642</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -44423,7 +44423,7 @@
         <v>-0.18167805818432164</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -44506,7 +44506,7 @@
         <v>-0.73052453371612514</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -44589,7 +44589,7 @@
         <v>-1.5009826760444123E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -44672,7 +44672,7 @@
         <v>-0.15860070411137861</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -44755,7 +44755,7 @@
         <v>-0.13730456798862051</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -44838,7 +44838,7 @@
         <v>0.36839082356962832</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -44921,7 +44921,7 @@
         <v>0.18245761903417482</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -45004,7 +45004,7 @@
         <v>0.22742473480474143</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -45087,7 +45087,7 @@
         <v>-3.2943145724916648E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -45170,7 +45170,7 @@
         <v>-0.22637920635014494</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -45253,7 +45253,7 @@
         <v>-0.26054650878898294</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -45336,7 +45336,7 @@
         <v>-0.11699798865364913</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -45419,7 +45419,7 @@
         <v>0.34963630090064257</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -45502,7 +45502,7 @@
         <v>-0.17279007194861853</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -45585,7 +45585,7 @@
         <v>-0.78430854703951447</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -45668,7 +45668,7 @@
         <v>-1.5923976692796063E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -45751,7 +45751,7 @@
         <v>-0.16803320521638915</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -45834,7 +45834,7 @@
         <v>-0.13354300735013738</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -45917,7 +45917,7 @@
         <v>0.40066736701528766</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -46000,7 +46000,7 @@
         <v>0.18382947054603144</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -46083,7 +46083,7 @@
         <v>0.2406992658908256</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -46166,7 +46166,7 @@
         <v>-3.5585336327689121E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -46249,7 +46249,7 @@
         <v>-0.20896388103592764</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -46332,7 +46332,7 @@
         <v>-0.27406735598634852</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -46415,7 +46415,7 @@
         <v>-0.11233777161752428</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -46498,7 +46498,7 @@
         <v>0.32548686065234889</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -46581,7 +46581,7 @@
         <v>0.21888830163862186</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -46664,7 +46664,7 @@
         <v>-3.5272270856435729E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -46747,7 +46747,7 @@
         <v>-0.20031496104475072</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -46830,7 +46830,7 @@
         <v>-0.28323005944518853</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -46913,7 +46913,7 @@
         <v>-0.12143617811566067</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -46996,7 +46996,7 @@
         <v>0.33277688952051449</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -47079,7 +47079,7 @@
         <v>-0.16502112180551265</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -47162,7 +47162,7 @@
         <v>-0.80624253037920024</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -47245,7 +47245,7 @@
         <v>-1.5421612694464655E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -47328,7 +47328,7 @@
         <v>-0.16208131145492288</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -47411,7 +47411,7 @@
         <v>-0.13091245446272495</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -47494,7 +47494,7 @@
         <v>0.35947356602414998</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -47577,7 +47577,7 @@
         <v>0.16985537032829737</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -47660,7 +47660,7 @@
         <v>0.22507598645748134</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -47743,7 +47743,7 @@
         <v>-3.1997908184051932E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -47826,7 +47826,7 @@
         <v>-0.20988415174255701</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -47909,7 +47909,7 @@
         <v>-0.2796749754294815</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -47992,7 +47992,7 @@
         <v>-0.11288777572189508</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -48075,7 +48075,7 @@
         <v>0.32229740285695407</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -48158,7 +48158,7 @@
         <v>-0.16773482769106485</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -48241,7 +48241,7 @@
         <v>-0.82928999105755041</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -48324,7 +48324,7 @@
         <v>-1.4860788120205935E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -48407,7 +48407,7 @@
         <v>-0.16161192709571529</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -48490,7 +48490,7 @@
         <v>-0.13035772393242473</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -48573,7 +48573,7 @@
         <v>0.36650325620326013</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -48656,7 +48656,7 @@
         <v>0.19318789433785161</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -48739,7 +48739,7 @@
         <v>0.22473047552438052</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -48822,7 +48822,7 @@
         <v>-3.206094483016203E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -48905,7 +48905,7 @@
         <v>-0.20327853343157756</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -48988,7 +48988,7 @@
         <v>-0.26648446469407749</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -49071,7 +49071,7 @@
         <v>-0.1122573573137703</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -49154,7 +49154,7 @@
         <v>0.33023862951028665</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -49237,7 +49237,7 @@
         <v>0.34129538164225937</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -49320,7 +49320,7 @@
         <v>5.3833481319321141E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -49403,7 +49403,7 @@
         <v>-0.178702442907301</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -49486,7 +49486,7 @@
         <v>-0.25843427198662428</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -49569,7 +49569,7 @@
         <v>-3.3323073312274763E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -49652,7 +49652,7 @@
         <v>0.40320032542354517</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -49735,7 +49735,7 @@
         <v>-0.15263910926371257</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -49818,7 +49818,7 @@
         <v>-0.82565871664279178</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -49901,7 +49901,7 @@
         <v>-9.0170305740912161E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -49984,7 +49984,7 @@
         <v>-8.9625737462220023E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -50067,7 +50067,7 @@
         <v>-0.12162824610174412</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -50150,7 +50150,7 @@
         <v>0.46297428949727881</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -50233,7 +50233,7 @@
         <v>0.20938376872673248</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -50316,7 +50316,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -50399,7 +50399,7 @@
         <v>5.6053418693313766E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -50482,7 +50482,7 @@
         <v>-0.18246459960008629</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -50565,7 +50565,7 @@
         <v>-0.25316010317057075</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -50648,7 +50648,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -50731,7 +50731,7 @@
         <v>0.42377177059821586</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -50814,7 +50814,7 @@
         <v>-0.14522944376547409</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -50897,7 +50897,7 @@
         <v>-0.8686617748012706</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -50980,7 +50980,7 @@
         <v>-8.7569239229155077E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -51063,7 +51063,7 @@
         <v>-9.6027575852378602E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -51146,7 +51146,7 @@
         <v>-0.11461123190356658</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -51229,7 +51229,7 @@
         <v>0.49604388160422735</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -51312,7 +51312,7 @@
         <v>0.20523755548461897</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -51395,7 +51395,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -51478,7 +51478,7 @@
         <v>5.6608403036811925E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -51561,7 +51561,7 @@
         <v>-0.19751322637122745</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -51644,7 +51644,7 @@
         <v>-0.27425677843478496</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -51727,7 +51727,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -51810,7 +51810,7 @@
         <v>0.4196574815632817</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -51893,7 +51893,7 @@
         <v>0.34119500064765867</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -51976,7 +51976,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -52059,7 +52059,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -52142,7 +52142,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -52225,7 +52225,7 @@
         <v>-3.1053930701010334E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -52308,7 +52308,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -52391,7 +52391,7 @@
         <v>-0.15569189144898682</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -52474,7 +52474,7 @@
         <v>-0.92129751798724857</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -52557,7 +52557,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -52640,7 +52640,7 @@
         <v>-9.6082448752865673E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -52723,7 +52723,7 @@
         <v>-0.12166333117273501</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -52806,7 +52806,7 @@
         <v>0.46713160964786665</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -52889,7 +52889,7 @@
         <v>0.21780058160822294</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -52972,7 +52972,7 @@
         <v>0.33774858649970252</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -53055,7 +53055,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -53138,7 +53138,7 @@
         <v>-0.19375106967844216</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -53221,7 +53221,7 @@
         <v>-0.26618730014622299</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -53304,7 +53304,7 @@
         <v>-3.1707697663136865E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -53387,7 +53387,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -53470,7 +53470,7 @@
         <v>-0.14653354489316406</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -53553,7 +53553,7 @@
         <v>-0.93015614796789525</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -53636,7 +53636,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -53719,7 +53719,7 @@
         <v>-9.7024433544560432E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -53802,7 +53802,7 @@
         <v>-0.12407250604744263</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -53885,7 +53885,7 @@
         <v>0.49632733525085837</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -53968,7 +53968,7 @@
         <v>0.21352998196884601</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -54051,7 +54051,7 @@
         <v>0.3549806572394833</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -54134,7 +54134,7 @@
         <v>5.8878289001719382E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -54217,7 +54217,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -54300,7 +54300,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -54383,7 +54383,7 @@
         <v>-3.33421150684532E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -54466,7 +54466,7 @@
         <v>0.4068208997742872</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -54549,7 +54549,7 @@
         <v>0.33446947400941418</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -54632,7 +54632,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -54715,7 +54715,7 @@
         <v>-0.182276491765447</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -54798,7 +54798,7 @@
         <v>-0.27699934621913286</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -54881,7 +54881,7 @@
         <v>-3.2361464625263403E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -54964,7 +54964,7 @@
         <v>0.39908603638861101</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -55047,7 +55047,7 @@
         <v>-0.15115717616406488</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -55130,7 +55130,7 @@
         <v>-0.80914554230993596</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -55213,7 +55213,7 @@
         <v>-8.406646965998887E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -55296,7 +55296,7 @@
         <v>-8.7824077229561093E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -55379,7 +55379,7 @@
         <v>-0.12048213378270846</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -55462,7 +55462,7 @@
         <v>0.46769851694112857</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -55545,7 +55545,7 @@
         <v>0.1970280532652342</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -55628,7 +55628,7 @@
         <v>0.33125728218219291</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -55711,7 +55711,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -55794,7 +55794,7 @@
         <v>-0.18611389159208799</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -55877,7 +55877,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -55960,7 +55960,7 @@
         <v>-3.2688348106326669E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -56043,7 +56043,7 @@
         <v>0.39497174735367691</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -56126,7 +56126,7 @@
         <v>-0.148178490633773</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -56209,7 +56209,7 @@
         <v>-0.85971713870430699</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -56292,7 +56292,7 @@
         <v>-8.6667536171745954E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -56375,7 +56375,7 @@
         <v>-8.8674607187110732E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -56458,7 +56458,7 @@
         <v>-0.1134651195845309</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -56541,7 +56541,7 @@
         <v>0.46741506329449761</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -56624,7 +56624,7 @@
         <v>0.20731066210567572</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -56707,7 +56707,7 @@
         <v>0.33105652019299159</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -56790,7 +56790,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -56873,7 +56873,7 @@
         <v>-0.18434567794647894</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -56956,7 +56956,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -57039,7 +57039,7 @@
         <v>-3.265661184602927E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -57122,7 +57122,7 @@
         <v>0.41126433193201606</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -57205,7 +57205,7 @@
         <v>0.19741312877482328</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -57288,7 +57288,7 @@
         <v>-5.5509142443077385E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -57371,7 +57371,7 @@
         <v>-0.23134604557356478</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -57454,7 +57454,7 @@
         <v>-0.25544176041861333</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -57537,7 +57537,7 @@
         <v>-0.16270967775809597</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -57620,7 +57620,7 @@
         <v>0.28175225412934646</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -57703,7 +57703,7 @@
         <v>-0.16598751427602706</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -57786,7 +57786,7 @@
         <v>-0.78959093885493115</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -57869,7 +57869,7 @@
         <v>-1.7461412185552319E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -57952,7 +57952,7 @@
         <v>-0.20535899678772981</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -58035,7 +58035,7 @@
         <v>-0.15839849252461777</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -58118,7 +58118,7 @@
         <v>0.35245854912687019</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -58201,7 +58201,7 @@
         <v>0.16081225716204761</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -58284,7 +58284,7 @@
         <v>0.18153397104662145</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -58367,7 +58367,7 @@
         <v>-5.3909329683069378E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -58450,7 +58450,7 @@
         <v>-0.23080100618241389</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -58533,7 +58533,7 @@
         <v>-0.27885065903039274</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -58616,7 +58616,7 @@
         <v>-0.16569544452305959</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -58699,7 +58699,7 @@
         <v>0.28621185639236219</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -58782,7 +58782,7 @@
         <v>-0.17556626662073285</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -58865,7 +58865,7 @@
         <v>-0.81163218696209283</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -58948,7 +58948,7 @@
         <v>-1.8636473990565453E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -59031,7 +59031,7 @@
         <v>-0.20315565508373407</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -59114,7 +59114,7 @@
         <v>-0.1452795221048481</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -59197,7 +59197,7 @@
         <v>0.33261161368040337</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -59280,7 +59280,7 @@
         <v>0.15937158615163902</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -59363,7 +59363,7 @@
         <v>0.18582768868086444</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -59446,7 +59446,7 @@
         <v>-5.5020829672942043E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -59529,7 +59529,7 @@
         <v>-0.23222911792352124</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -59612,7 +59612,7 @@
         <v>-0.30671134309338133</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -59695,7 +59695,7 @@
         <v>-0.14803193051300698</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -59778,7 +59778,7 @@
         <v>0.28914801574595983</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -59861,7 +59861,7 @@
         <v>0.17598171361019971</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -59944,7 +59944,7 @@
         <v>-4.9841411421543011E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -60027,7 +60027,7 @@
         <v>-0.22467411938961626</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -60110,7 +60110,7 @@
         <v>-0.26521910394337467</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -60193,7 +60193,7 @@
         <v>-0.15892035534779669</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -60276,7 +60276,7 @@
         <v>0.28807906682082157</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -60359,7 +60359,7 @@
         <v>-0.18183163125384061</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -60442,7 +60442,7 @@
         <v>-0.77397826887815169</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -60525,7 +60525,7 @@
         <v>-1.7694522489840651E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -60608,7 +60608,7 @@
         <v>-0.21201497421934132</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -60691,7 +60691,7 @@
         <v>-0.14546822093702438</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -60774,7 +60774,7 @@
         <v>0.33574541709400801</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -60857,7 +60857,7 @@
         <v>0.17012409886981447</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -60940,7 +60940,7 @@
         <v>0.19069977867171825</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -61023,7 +61023,7 @@
         <v>-5.7210265799620144E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -61106,7 +61106,7 @@
         <v>-0.21563720722343019</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -61189,7 +61189,7 @@
         <v>-0.26837877793199727</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -61272,7 +61272,7 @@
         <v>-0.14771910888517525</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -61355,7 +61355,7 @@
         <v>0.28083148365021204</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -61438,7 +61438,7 @@
         <v>-0.17585624758952306</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -61521,7 +61521,7 @@
         <v>-0.78804596031672758</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -61604,7 +61604,7 @@
         <v>-1.835223675063001E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -61687,7 +61687,7 @@
         <v>-0.21786598903212359</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -61770,7 +61770,7 @@
         <v>-0.14572406395195864</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -61853,7 +61853,7 @@
         <v>0.31752753790946048</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -61936,7 +61936,7 @@
         <v>0.17169500899641987</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -62019,7 +62019,7 @@
         <v>0.18796596099810325</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -62102,7 +62102,7 @@
         <v>-5.952263758544904E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -62185,7 +62185,7 @@
         <v>-0.23767692657785158</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -62268,7 +62268,7 @@
         <v>-0.28650404464498619</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -62351,7 +62351,7 @@
         <v>-0.15915432150812536</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -62434,7 +62434,7 @@
         <v>0.2731966527474296</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -62517,7 +62517,7 @@
         <v>0.19501476988237185</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -62600,7 +62600,7 @@
         <v>-5.0348330939479588E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -62683,7 +62683,7 @@
         <v>-0.22990682674428603</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -62766,7 +62766,7 @@
         <v>-0.28824220798069622</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -62849,7 +62849,7 @@
         <v>-0.16801064454174258</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -62932,7 +62932,7 @@
         <v>0.28146715869081351</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -63015,7 +63015,7 @@
         <v>-0.19289441956836567</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -63098,7 +63098,7 @@
         <v>-0.69388881502398359</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -63181,7 +63181,7 @@
         <v>-1.9607210627353693E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -63264,7 +63264,7 @@
         <v>-0.20218513468733235</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -63347,7 +63347,7 @@
         <v>-0.15405864171055272</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -63430,7 +63430,7 @@
         <v>0.35124673238676496</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -63513,7 +63513,7 @@
         <v>0.17259242942294106</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -63596,7 +63596,7 @@
         <v>0.18638460350136357</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -63679,7 +63679,7 @@
         <v>-5.2206519974136147E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -63762,7 +63762,7 @@
         <v>-0.22911942200885815</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -63845,7 +63845,7 @@
         <v>-0.27316100913376912</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -63928,7 +63928,7 @@
         <v>-0.16040620618731405</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -64011,7 +64011,7 @@
         <v>0.2995399215497494</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -64094,7 +64094,7 @@
         <v>-0.1733083373249055</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -64177,7 +64177,7 @@
         <v>-0.74294745728710343</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -64260,7 +64260,7 @@
         <v>-1.7942174565296207E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -64343,7 +64343,7 @@
         <v>-0.21312340680918018</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -64426,7 +64426,7 @@
         <v>-0.14504668087687686</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -64509,7 +64509,7 @@
         <v>0.35652131667585779</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -64592,7 +64592,7 @@
         <v>0.17599845361741759</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -64675,7 +64675,7 @@
         <v>0.17351496840262656</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -64758,7 +64758,7 @@
         <v>-5.3810493598558315E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -64841,7 +64841,7 @@
         <v>-0.22489861421211996</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -64924,7 +64924,7 @@
         <v>-0.27287552780237123</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -65007,7 +65007,7 @@
         <v>-0.15444732521633295</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -65098,9 +65098,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC7B88F-64DB-4C68-8FFC-305A2A41AB55}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -65183,7 +65183,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -65266,7 +65266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -65349,7 +65349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -65432,7 +65432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -65515,7 +65515,7 @@
         <v>0.5335206744279406</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -65598,7 +65598,7 @@
         <v>0.49739060618225611</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -65681,7 +65681,7 @@
         <v>0.40405459654757125</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -65764,7 +65764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -65847,7 +65847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -65930,7 +65930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -66013,7 +66013,7 @@
         <v>0.36852669610598154</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -66096,7 +66096,7 @@
         <v>0.23966278602970695</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -66179,7 +66179,7 @@
         <v>0.30931352870333201</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -66262,7 +66262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -66345,7 +66345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -66428,7 +66428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -66511,7 +66511,7 @@
         <v>0.4676836611802489</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -66594,7 +66594,7 @@
         <v>0.17442794058611</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -66677,7 +66677,7 @@
         <v>0.34263348052990766</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -66760,7 +66760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -66843,7 +66843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -66926,7 +66926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -67009,7 +67009,7 @@
         <v>0.44439983942191891</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -67092,7 +67092,7 @@
         <v>0.50040144520272978</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -67183,9 +67183,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBBB125-439E-474E-9960-563C78F44B33}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -67268,7 +67268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -67351,7 +67351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -67434,7 +67434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -67517,7 +67517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -67600,7 +67600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -67683,7 +67683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -67766,7 +67766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -67849,7 +67849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -67932,7 +67932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -68015,7 +68015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -68098,7 +68098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -68181,7 +68181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -68264,7 +68264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -68347,7 +68347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -68430,7 +68430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -68513,7 +68513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -68596,7 +68596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -68679,7 +68679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -68762,7 +68762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -68845,7 +68845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -68928,7 +68928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -69011,7 +69011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -69094,7 +69094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -69177,7 +69177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -69268,13 +69268,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -69357,7 +69357,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -69440,7 +69440,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -69523,7 +69523,7 @@
         <v>-9.797600000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -69606,7 +69606,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -69689,7 +69689,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -69772,7 +69772,7 @@
         <v>-9.4056960000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -69855,7 +69855,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -69938,7 +69938,7 @@
         <v>4.3249919999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -70021,7 +70021,7 @@
         <v>-9.8759808000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -70104,7 +70104,7 @@
         <v>9.9170400000000036</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -70187,7 +70187,7 @@
         <v>4.2799399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -70270,7 +70270,7 @@
         <v>-9.6784611839999997</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -70353,7 +70353,7 @@
         <v>10.115380800000004</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -70436,7 +70436,7 @@
         <v>4.1943412000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -70519,7 +70519,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -70602,7 +70602,7 @@
         <v>9.7107655680000047</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -70685,7 +70685,7 @@
         <v>4.1104543759999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -70768,7 +70768,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -70851,7 +70851,7 @@
         <v>9.4194426009600036</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -70934,7 +70934,7 @@
         <v>4.7079339999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -71017,7 +71017,7 @@
         <v>-10.367567620300798</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -71100,7 +71100,7 @@
         <v>9.5136370269696027</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -71183,7 +71183,7 @@
         <v>4.8020926800000003</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -71266,7 +71266,7 @@
         <v>-10.263891944097791</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -71349,7 +71349,7 @@
         <v>9.7990461377786904</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -71432,7 +71432,7 @@
         <v>4.9461554604</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -71515,7 +71515,7 @@
         <v>-10.469169782979748</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -71598,7 +71598,7 @@
         <v>9.5050747536453297</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -71681,7 +71681,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -71764,7 +71764,7 @@
         <v>-10.992628272128735</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -71847,7 +71847,7 @@
         <v>9.6001255011817825</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -71930,7 +71930,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -72013,7 +72013,7 @@
         <v>-10.552923141243587</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -72096,7 +72096,7 @@
         <v>9.888129266217236</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -72179,7 +72179,7 @@
         <v>4.4278119270000005</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -72262,7 +72262,7 @@
         <v>-10.341864678418714</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>

--- a/data/CS7/case33_1/case33_1_operational_data.xlsx
+++ b/data/CS7/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BC551E-CC7F-244D-969E-3FD8615CF118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C614731-E163-634C-8926-8FFCC4133114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52180" yWindow="1260" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,10 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <f>E2*3.5</f>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
-        <v>2.4</v>
+        <f>F2*3.5</f>
+        <v>8.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -493,10 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*3.5</f>
+        <v>12.599999999999998</v>
       </c>
       <c r="C3" s="1">
-        <v>1.6</v>
+        <f t="shared" ref="C3:C33" si="1">F3*3.5</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -513,10 +517,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C4" s="1">
-        <v>3.2</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -533,10 +539,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -553,10 +561,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C6" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -573,10 +583,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -593,10 +605,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -613,10 +627,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C9" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -633,10 +649,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C10" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -653,10 +671,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>6.2999999999999989</v>
       </c>
       <c r="C11" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -673,10 +693,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C12" s="1">
-        <v>1.4000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -693,10 +715,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C13" s="1">
-        <v>1.4000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -713,10 +737,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C14" s="1">
-        <v>3.2</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -733,10 +759,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C15" s="1">
-        <v>0.4</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -753,10 +781,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C16" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -773,10 +803,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C17" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -793,10 +825,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C18" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -813,10 +847,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C19" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -833,10 +869,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C20" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -853,10 +891,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C21" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -873,10 +913,12 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C22" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -893,10 +935,12 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C23" s="1">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -913,10 +957,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C24" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -933,10 +979,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C25" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -953,10 +1001,12 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -973,10 +1023,12 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -993,10 +1045,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C28" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1013,10 +1067,12 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C29" s="1">
-        <v>2.8000000000000003</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1033,10 +1089,12 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1053,10 +1111,12 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>2.8000000000000003</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1073,10 +1133,12 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>8.4</v>
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
       </c>
       <c r="C32" s="1">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1093,10 +1155,12 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C33" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
